--- a/WjEff.xlsx
+++ b/WjEff.xlsx
@@ -19,12 +19,13 @@
     <sheet name="07-02-26" sheetId="12" r:id="rId15"/>
     <sheet name="08-02-26" sheetId="13" r:id="rId16"/>
     <sheet name="09-02-26" sheetId="14" r:id="rId17"/>
+    <sheet name="10-02-26" sheetId="15" r:id="rId18"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="253">
   <si>
     <t>DAY</t>
   </si>
@@ -780,6 +781,9 @@
   </si>
   <si>
     <t>12;02</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> FLUTE </t>
   </si>
 </sst>
 </file>
@@ -866,7 +870,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -958,6 +962,12 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -8364,6 +8374,896 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:K30"/>
+  <sheetFormatPr defaultColWidth="9.16667" defaultRowHeight="15.4" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="2.67188" style="31" customWidth="1"/>
+    <col min="2" max="2" width="11" style="31" customWidth="1"/>
+    <col min="3" max="6" width="9.17188" style="31" customWidth="1"/>
+    <col min="7" max="7" width="9.85156" style="31" customWidth="1"/>
+    <col min="8" max="11" width="9.17188" style="31" customWidth="1"/>
+    <col min="12" max="16384" width="9.17188" style="31" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="22"/>
+      <c r="B1" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" t="s" s="23">
+        <v>1</v>
+      </c>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+    </row>
+    <row r="2" ht="28.1" customHeight="1">
+      <c r="A2" t="s" s="24">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s" s="6">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s" s="6">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s" s="7">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s" s="6">
+        <v>6</v>
+      </c>
+      <c r="F2" t="s" s="6">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s" s="25">
+        <v>3</v>
+      </c>
+      <c r="H2" t="s" s="25">
+        <v>4</v>
+      </c>
+      <c r="I2" t="s" s="26">
+        <v>5</v>
+      </c>
+      <c r="J2" t="s" s="25">
+        <v>6</v>
+      </c>
+      <c r="K2" t="s" s="25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="27">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s" s="6">
+        <v>8</v>
+      </c>
+      <c r="C3" s="9">
+        <v>11</v>
+      </c>
+      <c r="D3" s="9">
+        <v>10.23</v>
+      </c>
+      <c r="E3" s="9">
+        <v>29</v>
+      </c>
+      <c r="F3" s="9">
+        <v>547</v>
+      </c>
+      <c r="G3" t="s" s="25">
+        <v>8</v>
+      </c>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="28">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="27">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s" s="6">
+        <v>8</v>
+      </c>
+      <c r="C4" s="9">
+        <v>11</v>
+      </c>
+      <c r="D4" s="9">
+        <v>10.35</v>
+      </c>
+      <c r="E4" s="9">
+        <v>13</v>
+      </c>
+      <c r="F4" s="9">
+        <v>545</v>
+      </c>
+      <c r="G4" t="s" s="25">
+        <v>8</v>
+      </c>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="28">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="27">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s" s="6">
+        <v>8</v>
+      </c>
+      <c r="C5" s="9">
+        <v>11</v>
+      </c>
+      <c r="D5" s="9">
+        <v>10.43</v>
+      </c>
+      <c r="E5" s="9">
+        <v>18</v>
+      </c>
+      <c r="F5" s="9">
+        <v>543</v>
+      </c>
+      <c r="G5" t="s" s="25">
+        <v>8</v>
+      </c>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="32"/>
+      <c r="K5" s="28">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="27">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s" s="6">
+        <v>17</v>
+      </c>
+      <c r="C6" s="9">
+        <v>3.29</v>
+      </c>
+      <c r="D6" s="9">
+        <v>3.02</v>
+      </c>
+      <c r="E6" s="9">
+        <v>12</v>
+      </c>
+      <c r="F6" s="9">
+        <v>545</v>
+      </c>
+      <c r="G6" t="s" s="25">
+        <v>17</v>
+      </c>
+      <c r="H6" s="32"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="32"/>
+      <c r="K6" s="28">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="27">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s" s="6">
+        <v>17</v>
+      </c>
+      <c r="C7" s="9">
+        <v>11</v>
+      </c>
+      <c r="D7" s="9">
+        <v>10.18</v>
+      </c>
+      <c r="E7" s="9">
+        <v>27</v>
+      </c>
+      <c r="F7" s="9">
+        <v>545</v>
+      </c>
+      <c r="G7" t="s" s="25">
+        <v>17</v>
+      </c>
+      <c r="H7" s="32"/>
+      <c r="I7" s="32"/>
+      <c r="J7" s="32"/>
+      <c r="K7" s="28">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="27">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s" s="6">
+        <v>17</v>
+      </c>
+      <c r="C8" s="9">
+        <v>10.59</v>
+      </c>
+      <c r="D8" s="9">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="E8" s="9">
+        <v>78</v>
+      </c>
+      <c r="F8" s="9">
+        <v>548</v>
+      </c>
+      <c r="G8" t="s" s="25">
+        <v>17</v>
+      </c>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="28">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="27">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s" s="6">
+        <v>8</v>
+      </c>
+      <c r="C9" s="9">
+        <v>11</v>
+      </c>
+      <c r="D9" s="9">
+        <v>10.4</v>
+      </c>
+      <c r="E9" s="9">
+        <v>8</v>
+      </c>
+      <c r="F9" s="9">
+        <v>699</v>
+      </c>
+      <c r="G9" t="s" s="25">
+        <v>8</v>
+      </c>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="28">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="27">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s" s="6">
+        <v>8</v>
+      </c>
+      <c r="C10" s="9">
+        <v>11</v>
+      </c>
+      <c r="D10" s="9">
+        <v>10.12</v>
+      </c>
+      <c r="E10" s="9">
+        <v>28</v>
+      </c>
+      <c r="F10" s="9">
+        <v>699</v>
+      </c>
+      <c r="G10" t="s" s="25">
+        <v>8</v>
+      </c>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="28">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="27">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s" s="6">
+        <v>8</v>
+      </c>
+      <c r="C11" s="9">
+        <v>11</v>
+      </c>
+      <c r="D11" s="9">
+        <v>10.52</v>
+      </c>
+      <c r="E11" s="9">
+        <v>14</v>
+      </c>
+      <c r="F11" s="9">
+        <v>699</v>
+      </c>
+      <c r="G11" t="s" s="25">
+        <v>8</v>
+      </c>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="28">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="27">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s" s="6">
+        <v>8</v>
+      </c>
+      <c r="C12" s="9">
+        <v>11</v>
+      </c>
+      <c r="D12" s="9">
+        <v>10.5</v>
+      </c>
+      <c r="E12" s="9">
+        <v>10</v>
+      </c>
+      <c r="F12" s="9">
+        <v>699</v>
+      </c>
+      <c r="G12" t="s" s="25">
+        <v>8</v>
+      </c>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="28">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s" s="6">
+        <v>8</v>
+      </c>
+      <c r="C13" s="9">
+        <v>11</v>
+      </c>
+      <c r="D13" s="9">
+        <v>10.41</v>
+      </c>
+      <c r="E13" s="9">
+        <v>13</v>
+      </c>
+      <c r="F13" s="9">
+        <v>699</v>
+      </c>
+      <c r="G13" t="s" s="25">
+        <v>8</v>
+      </c>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="28">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="27">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s" s="6">
+        <v>8</v>
+      </c>
+      <c r="C14" s="9">
+        <v>11</v>
+      </c>
+      <c r="D14" s="9">
+        <v>10.3</v>
+      </c>
+      <c r="E14" s="9">
+        <v>15</v>
+      </c>
+      <c r="F14" s="9">
+        <v>649</v>
+      </c>
+      <c r="G14" t="s" s="25">
+        <v>8</v>
+      </c>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="28">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="27">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s" s="6">
+        <v>8</v>
+      </c>
+      <c r="C15" s="9">
+        <v>11</v>
+      </c>
+      <c r="D15" s="9">
+        <v>10.24</v>
+      </c>
+      <c r="E15" s="9">
+        <v>22</v>
+      </c>
+      <c r="F15" s="9">
+        <v>699</v>
+      </c>
+      <c r="G15" t="s" s="25">
+        <v>8</v>
+      </c>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="28">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="27">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s" s="6">
+        <v>8</v>
+      </c>
+      <c r="C16" s="9">
+        <v>11</v>
+      </c>
+      <c r="D16" s="9">
+        <v>10.29</v>
+      </c>
+      <c r="E16" s="9">
+        <v>24</v>
+      </c>
+      <c r="F16" s="9">
+        <v>699</v>
+      </c>
+      <c r="G16" t="s" s="25">
+        <v>8</v>
+      </c>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="32"/>
+      <c r="K16" s="28">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="27">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s" s="6">
+        <v>8</v>
+      </c>
+      <c r="C17" s="9">
+        <v>11</v>
+      </c>
+      <c r="D17" s="9">
+        <v>10.49</v>
+      </c>
+      <c r="E17" s="9">
+        <v>18</v>
+      </c>
+      <c r="F17" s="9">
+        <v>698</v>
+      </c>
+      <c r="G17" t="s" s="25">
+        <v>8</v>
+      </c>
+      <c r="H17" s="32"/>
+      <c r="I17" s="32"/>
+      <c r="J17" s="32"/>
+      <c r="K17" s="28">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="27">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s" s="6">
+        <v>8</v>
+      </c>
+      <c r="C18" s="9">
+        <v>11</v>
+      </c>
+      <c r="D18" s="9">
+        <v>10.11</v>
+      </c>
+      <c r="E18" s="9">
+        <v>37</v>
+      </c>
+      <c r="F18" s="9">
+        <v>699</v>
+      </c>
+      <c r="G18" t="s" s="25">
+        <v>8</v>
+      </c>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="32"/>
+      <c r="K18" s="28">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="27">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s" s="6">
+        <v>8</v>
+      </c>
+      <c r="C19" s="9">
+        <v>11</v>
+      </c>
+      <c r="D19" s="9">
+        <v>10.24</v>
+      </c>
+      <c r="E19" s="9">
+        <v>30</v>
+      </c>
+      <c r="F19" s="9">
+        <v>699</v>
+      </c>
+      <c r="G19" t="s" s="25">
+        <v>8</v>
+      </c>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="32"/>
+      <c r="K19" s="28">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="27">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s" s="6">
+        <v>17</v>
+      </c>
+      <c r="C20" s="9">
+        <v>10.58</v>
+      </c>
+      <c r="D20" s="9">
+        <v>10.32</v>
+      </c>
+      <c r="E20" s="9">
+        <v>23</v>
+      </c>
+      <c r="F20" s="9">
+        <v>611</v>
+      </c>
+      <c r="G20" t="s" s="25">
+        <v>17</v>
+      </c>
+      <c r="H20" s="32"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="28">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="27">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s" s="6">
+        <v>17</v>
+      </c>
+      <c r="C21" s="9">
+        <v>10.52</v>
+      </c>
+      <c r="D21" s="9">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="E21" s="9">
+        <v>56</v>
+      </c>
+      <c r="F21" s="9">
+        <v>604</v>
+      </c>
+      <c r="G21" t="s" s="25">
+        <v>17</v>
+      </c>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="28">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="27">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s" s="6">
+        <v>252</v>
+      </c>
+      <c r="C22" s="9">
+        <v>10.49</v>
+      </c>
+      <c r="D22" s="9">
+        <v>10.29</v>
+      </c>
+      <c r="E22" s="9">
+        <v>14</v>
+      </c>
+      <c r="F22" s="9">
+        <v>542</v>
+      </c>
+      <c r="G22" t="s" s="25">
+        <v>8</v>
+      </c>
+      <c r="H22" s="32"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="32"/>
+      <c r="K22" s="28">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="27">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s" s="6">
+        <v>8</v>
+      </c>
+      <c r="C23" s="9">
+        <v>11</v>
+      </c>
+      <c r="D23" s="9">
+        <v>10.44</v>
+      </c>
+      <c r="E23" s="9">
+        <v>8</v>
+      </c>
+      <c r="F23" s="9">
+        <v>549</v>
+      </c>
+      <c r="G23" t="s" s="25">
+        <v>8</v>
+      </c>
+      <c r="H23" s="32"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="28">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="27">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s" s="6">
+        <v>8</v>
+      </c>
+      <c r="C24" s="9">
+        <v>11</v>
+      </c>
+      <c r="D24" s="9">
+        <v>10.51</v>
+      </c>
+      <c r="E24" s="9">
+        <v>7</v>
+      </c>
+      <c r="F24" s="9">
+        <v>546</v>
+      </c>
+      <c r="G24" t="s" s="25">
+        <v>8</v>
+      </c>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="28">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="27">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s" s="6">
+        <v>8</v>
+      </c>
+      <c r="C25" s="9">
+        <v>11</v>
+      </c>
+      <c r="D25" s="9">
+        <v>10.35</v>
+      </c>
+      <c r="E25" s="9">
+        <v>18</v>
+      </c>
+      <c r="F25" s="9">
+        <v>698</v>
+      </c>
+      <c r="G25" t="s" s="25">
+        <v>8</v>
+      </c>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="32"/>
+      <c r="K25" s="28">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="27">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s" s="6">
+        <v>17</v>
+      </c>
+      <c r="C26" s="9">
+        <v>11</v>
+      </c>
+      <c r="D26" s="9">
+        <v>10.39</v>
+      </c>
+      <c r="E26" s="9">
+        <v>21</v>
+      </c>
+      <c r="F26" s="9">
+        <v>698</v>
+      </c>
+      <c r="G26" t="s" s="25">
+        <v>17</v>
+      </c>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="28">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="27">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s" s="6">
+        <v>17</v>
+      </c>
+      <c r="C27" s="9">
+        <v>10.52</v>
+      </c>
+      <c r="D27" s="9">
+        <v>9.57</v>
+      </c>
+      <c r="E27" s="9">
+        <v>41</v>
+      </c>
+      <c r="F27" s="9">
+        <v>699</v>
+      </c>
+      <c r="G27" t="s" s="25">
+        <v>17</v>
+      </c>
+      <c r="H27" s="32"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="28">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="27">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s" s="6">
+        <v>17</v>
+      </c>
+      <c r="C28" s="9">
+        <v>10.55</v>
+      </c>
+      <c r="D28" s="9">
+        <v>10.12</v>
+      </c>
+      <c r="E28" s="9">
+        <v>40</v>
+      </c>
+      <c r="F28" s="9">
+        <v>699</v>
+      </c>
+      <c r="G28" t="s" s="25">
+        <v>17</v>
+      </c>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="28">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="27">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s" s="6">
+        <v>17</v>
+      </c>
+      <c r="C29" s="9">
+        <v>10.54</v>
+      </c>
+      <c r="D29" s="9">
+        <v>10.22</v>
+      </c>
+      <c r="E29" s="9">
+        <v>27</v>
+      </c>
+      <c r="F29" s="9">
+        <v>699</v>
+      </c>
+      <c r="G29" t="s" s="25">
+        <v>17</v>
+      </c>
+      <c r="H29" s="32"/>
+      <c r="I29" s="32"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="28">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="27">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s" s="6">
+        <v>17</v>
+      </c>
+      <c r="C30" s="9">
+        <v>10.56</v>
+      </c>
+      <c r="D30" s="9">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="E30" s="9">
+        <v>37</v>
+      </c>
+      <c r="F30" s="9">
+        <v>699</v>
+      </c>
+      <c r="G30" t="s" s="25">
+        <v>17</v>
+      </c>
+      <c r="H30" s="32"/>
+      <c r="I30" s="32"/>
+      <c r="J30" s="32"/>
+      <c r="K30" s="28">
+        <v>699</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="G1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:K30"/>

--- a/WjEff.xlsx
+++ b/WjEff.xlsx
@@ -783,7 +783,7 @@
     <t>12;02</t>
   </si>
   <si>
-    <t xml:space="preserve"> FLUTE </t>
+    <t>KASAB FLUTE</t>
   </si>
 </sst>
 </file>
@@ -870,7 +870,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -965,9 +965,6 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -8461,9 +8458,15 @@
       <c r="G3" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
+      <c r="H3" s="28">
+        <v>13</v>
+      </c>
+      <c r="I3" s="28">
+        <v>11.33</v>
+      </c>
+      <c r="J3" s="28">
+        <v>46</v>
+      </c>
       <c r="K3" s="28">
         <v>547</v>
       </c>
@@ -8490,9 +8493,15 @@
       <c r="G4" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="32"/>
+      <c r="H4" s="28">
+        <v>13</v>
+      </c>
+      <c r="I4" s="28">
+        <v>12.34</v>
+      </c>
+      <c r="J4" s="28">
+        <v>10</v>
+      </c>
       <c r="K4" s="28">
         <v>547</v>
       </c>
@@ -8519,9 +8528,15 @@
       <c r="G5" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="32"/>
+      <c r="H5" s="28">
+        <v>13</v>
+      </c>
+      <c r="I5" s="28">
+        <v>12.22</v>
+      </c>
+      <c r="J5" s="28">
+        <v>21</v>
+      </c>
       <c r="K5" s="28">
         <v>544</v>
       </c>
@@ -8548,9 +8563,15 @@
       <c r="G6" t="s" s="25">
         <v>17</v>
       </c>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
-      <c r="J6" s="32"/>
+      <c r="H6" s="28">
+        <v>3.29</v>
+      </c>
+      <c r="I6" s="28">
+        <v>3.02</v>
+      </c>
+      <c r="J6" s="28">
+        <v>12</v>
+      </c>
       <c r="K6" s="28">
         <v>545</v>
       </c>
@@ -8577,9 +8598,15 @@
       <c r="G7" t="s" s="25">
         <v>17</v>
       </c>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="32"/>
+      <c r="H7" s="28">
+        <v>12.57</v>
+      </c>
+      <c r="I7" s="28">
+        <v>11.59</v>
+      </c>
+      <c r="J7" s="28">
+        <v>31</v>
+      </c>
       <c r="K7" s="28">
         <v>546</v>
       </c>
@@ -8606,9 +8633,15 @@
       <c r="G8" t="s" s="25">
         <v>17</v>
       </c>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="H8" s="28">
+        <v>12</v>
+      </c>
+      <c r="I8" s="28">
+        <v>7.31</v>
+      </c>
+      <c r="J8" s="28">
+        <v>61</v>
+      </c>
       <c r="K8" s="28">
         <v>549</v>
       </c>
@@ -8635,9 +8668,15 @@
       <c r="G9" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="H9" s="28">
+        <v>12.48</v>
+      </c>
+      <c r="I9" s="28">
+        <v>12.15</v>
+      </c>
+      <c r="J9" s="28">
+        <v>12</v>
+      </c>
       <c r="K9" s="28">
         <v>699</v>
       </c>
@@ -8664,9 +8703,15 @@
       <c r="G10" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="H10" s="28">
+        <v>13</v>
+      </c>
+      <c r="I10" s="28">
+        <v>12.27</v>
+      </c>
+      <c r="J10" s="28">
+        <v>14</v>
+      </c>
       <c r="K10" s="28">
         <v>699</v>
       </c>
@@ -8693,9 +8738,15 @@
       <c r="G11" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="H11" s="28">
+        <v>12.44</v>
+      </c>
+      <c r="I11" s="28">
+        <v>12.2</v>
+      </c>
+      <c r="J11" s="28">
+        <v>16</v>
+      </c>
       <c r="K11" s="28">
         <v>699</v>
       </c>
@@ -8722,9 +8773,15 @@
       <c r="G12" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="32"/>
+      <c r="H12" s="28">
+        <v>12.54</v>
+      </c>
+      <c r="I12" s="28">
+        <v>12.43</v>
+      </c>
+      <c r="J12" s="28">
+        <v>12</v>
+      </c>
       <c r="K12" s="28">
         <v>698</v>
       </c>
@@ -8751,9 +8808,15 @@
       <c r="G13" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
+      <c r="H13" s="28">
+        <v>13</v>
+      </c>
+      <c r="I13" s="28">
+        <v>12.17</v>
+      </c>
+      <c r="J13" s="28">
+        <v>26</v>
+      </c>
       <c r="K13" s="28">
         <v>699</v>
       </c>
@@ -8780,9 +8843,15 @@
       <c r="G14" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="32"/>
+      <c r="H14" s="28">
+        <v>12.5</v>
+      </c>
+      <c r="I14" s="28">
+        <v>11.58</v>
+      </c>
+      <c r="J14" s="28">
+        <v>38</v>
+      </c>
       <c r="K14" s="28">
         <v>697</v>
       </c>
@@ -8809,9 +8878,15 @@
       <c r="G15" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
+      <c r="H15" s="28">
+        <v>12.48</v>
+      </c>
+      <c r="I15" s="28">
+        <v>12.04</v>
+      </c>
+      <c r="J15" s="28">
+        <v>29</v>
+      </c>
       <c r="K15" s="28">
         <v>699</v>
       </c>
@@ -8838,9 +8913,15 @@
       <c r="G16" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32"/>
+      <c r="H16" s="28">
+        <v>13</v>
+      </c>
+      <c r="I16" s="28">
+        <v>12.31</v>
+      </c>
+      <c r="J16" s="28">
+        <v>18</v>
+      </c>
       <c r="K16" s="28">
         <v>698</v>
       </c>
@@ -8867,9 +8948,15 @@
       <c r="G17" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="32"/>
+      <c r="H17" s="28">
+        <v>12.58</v>
+      </c>
+      <c r="I17" s="28">
+        <v>12.32</v>
+      </c>
+      <c r="J17" s="28">
+        <v>21</v>
+      </c>
       <c r="K17" s="28">
         <v>699</v>
       </c>
@@ -8896,9 +8983,15 @@
       <c r="G18" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="32"/>
+      <c r="H18" s="28">
+        <v>12.47</v>
+      </c>
+      <c r="I18" s="28">
+        <v>11.54</v>
+      </c>
+      <c r="J18" s="28">
+        <v>33</v>
+      </c>
       <c r="K18" s="28">
         <v>699</v>
       </c>
@@ -8925,9 +9018,15 @@
       <c r="G19" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="32"/>
+      <c r="H19" s="28">
+        <v>12.56</v>
+      </c>
+      <c r="I19" s="28">
+        <v>12.27</v>
+      </c>
+      <c r="J19" s="28">
+        <v>22</v>
+      </c>
       <c r="K19" s="28">
         <v>699</v>
       </c>
@@ -8954,9 +9053,15 @@
       <c r="G20" t="s" s="25">
         <v>17</v>
       </c>
-      <c r="H20" s="32"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="32"/>
+      <c r="H20" s="28">
+        <v>13</v>
+      </c>
+      <c r="I20" s="28">
+        <v>12.17</v>
+      </c>
+      <c r="J20" s="28">
+        <v>27</v>
+      </c>
       <c r="K20" s="28">
         <v>610</v>
       </c>
@@ -8983,9 +9088,15 @@
       <c r="G21" t="s" s="25">
         <v>17</v>
       </c>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
+      <c r="H21" s="28">
+        <v>12.54</v>
+      </c>
+      <c r="I21" s="28">
+        <v>11.21</v>
+      </c>
+      <c r="J21" s="28">
+        <v>52</v>
+      </c>
       <c r="K21" s="28">
         <v>604</v>
       </c>
@@ -8995,7 +9106,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s" s="6">
-        <v>252</v>
+        <v>8</v>
       </c>
       <c r="C22" s="9">
         <v>10.49</v>
@@ -9012,9 +9123,15 @@
       <c r="G22" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H22" s="32"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="32"/>
+      <c r="H22" s="28">
+        <v>13</v>
+      </c>
+      <c r="I22" s="28">
+        <v>12.49</v>
+      </c>
+      <c r="J22" s="28">
+        <v>11</v>
+      </c>
       <c r="K22" s="28">
         <v>542</v>
       </c>
@@ -9041,9 +9158,15 @@
       <c r="G23" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H23" s="32"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="32"/>
+      <c r="H23" s="28">
+        <v>13</v>
+      </c>
+      <c r="I23" s="28">
+        <v>12.4</v>
+      </c>
+      <c r="J23" s="28">
+        <v>15</v>
+      </c>
       <c r="K23" s="28">
         <v>549</v>
       </c>
@@ -9070,9 +9193,15 @@
       <c r="G24" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H24" s="32"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="32"/>
+      <c r="H24" s="28">
+        <v>13</v>
+      </c>
+      <c r="I24" s="28">
+        <v>12.42</v>
+      </c>
+      <c r="J24" s="28">
+        <v>12</v>
+      </c>
       <c r="K24" s="28">
         <v>546</v>
       </c>
@@ -9099,9 +9228,15 @@
       <c r="G25" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="32"/>
+      <c r="H25" s="28">
+        <v>12.36</v>
+      </c>
+      <c r="I25" s="28">
+        <v>12.08</v>
+      </c>
+      <c r="J25" s="28">
+        <v>18</v>
+      </c>
       <c r="K25" s="28">
         <v>698</v>
       </c>
@@ -9128,9 +9263,15 @@
       <c r="G26" t="s" s="25">
         <v>17</v>
       </c>
-      <c r="H26" s="32"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="32"/>
+      <c r="H26" s="28">
+        <v>12.44</v>
+      </c>
+      <c r="I26" s="28">
+        <v>11.53</v>
+      </c>
+      <c r="J26" s="28">
+        <v>46</v>
+      </c>
       <c r="K26" s="28">
         <v>699</v>
       </c>
@@ -9157,9 +9298,15 @@
       <c r="G27" t="s" s="25">
         <v>17</v>
       </c>
-      <c r="H27" s="32"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="32"/>
+      <c r="H27" s="28">
+        <v>12.39</v>
+      </c>
+      <c r="I27" s="28">
+        <v>12</v>
+      </c>
+      <c r="J27" s="28">
+        <v>30</v>
+      </c>
       <c r="K27" s="28">
         <v>699</v>
       </c>
@@ -9184,11 +9331,17 @@
         <v>699</v>
       </c>
       <c r="G28" t="s" s="25">
-        <v>17</v>
-      </c>
-      <c r="H28" s="32"/>
-      <c r="I28" s="32"/>
-      <c r="J28" s="32"/>
+        <v>252</v>
+      </c>
+      <c r="H28" s="28">
+        <v>4.49</v>
+      </c>
+      <c r="I28" s="28">
+        <v>2.25</v>
+      </c>
+      <c r="J28" s="28">
+        <v>80</v>
+      </c>
       <c r="K28" s="28">
         <v>698</v>
       </c>
@@ -9215,9 +9368,15 @@
       <c r="G29" t="s" s="25">
         <v>17</v>
       </c>
-      <c r="H29" s="32"/>
-      <c r="I29" s="32"/>
-      <c r="J29" s="32"/>
+      <c r="H29" s="28">
+        <v>10.46</v>
+      </c>
+      <c r="I29" s="28">
+        <v>8.23</v>
+      </c>
+      <c r="J29" s="28">
+        <v>106</v>
+      </c>
       <c r="K29" s="28">
         <v>699</v>
       </c>
@@ -9244,9 +9403,15 @@
       <c r="G30" t="s" s="25">
         <v>17</v>
       </c>
-      <c r="H30" s="32"/>
-      <c r="I30" s="32"/>
-      <c r="J30" s="32"/>
+      <c r="H30" s="28">
+        <v>13</v>
+      </c>
+      <c r="I30" s="28">
+        <v>12.11</v>
+      </c>
+      <c r="J30" s="28">
+        <v>23</v>
+      </c>
       <c r="K30" s="28">
         <v>699</v>
       </c>

--- a/WjEff.xlsx
+++ b/WjEff.xlsx
@@ -871,7 +871,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -969,9 +969,6 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -9523,9 +9520,15 @@
       <c r="G3" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
+      <c r="H3" s="28">
+        <v>12.51</v>
+      </c>
+      <c r="I3" s="28">
+        <v>11.19</v>
+      </c>
+      <c r="J3" s="28">
+        <v>39</v>
+      </c>
       <c r="K3" s="28">
         <v>547</v>
       </c>
@@ -9552,9 +9555,15 @@
       <c r="G4" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
+      <c r="H4" s="28">
+        <v>12.47</v>
+      </c>
+      <c r="I4" s="28">
+        <v>12.15</v>
+      </c>
+      <c r="J4" s="28">
+        <v>26</v>
+      </c>
       <c r="K4" s="28">
         <v>547</v>
       </c>
@@ -9581,9 +9590,15 @@
       <c r="G5" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
+      <c r="H5" s="28">
+        <v>13</v>
+      </c>
+      <c r="I5" s="28">
+        <v>11.53</v>
+      </c>
+      <c r="J5" s="28">
+        <v>45</v>
+      </c>
       <c r="K5" s="28">
         <v>544</v>
       </c>
@@ -9608,11 +9623,17 @@
         <v>545</v>
       </c>
       <c r="G6" t="s" s="25">
-        <v>17</v>
-      </c>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
+        <v>58</v>
+      </c>
+      <c r="H6" s="28">
+        <v>5.35</v>
+      </c>
+      <c r="I6" s="28">
+        <v>3.41</v>
+      </c>
+      <c r="J6" s="28">
+        <v>59</v>
+      </c>
       <c r="K6" s="28">
         <v>545</v>
       </c>
@@ -9639,9 +9660,15 @@
       <c r="G7" t="s" s="25">
         <v>17</v>
       </c>
-      <c r="H7" s="33"/>
-      <c r="I7" s="33"/>
-      <c r="J7" s="33"/>
+      <c r="H7" s="28">
+        <v>12.49</v>
+      </c>
+      <c r="I7" s="28">
+        <v>11.21</v>
+      </c>
+      <c r="J7" s="28">
+        <v>46</v>
+      </c>
       <c r="K7" s="28">
         <v>546</v>
       </c>
@@ -9668,9 +9695,15 @@
       <c r="G8" t="s" s="25">
         <v>17</v>
       </c>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
+      <c r="H8" s="28">
+        <v>13</v>
+      </c>
+      <c r="I8" s="28">
+        <v>11.57</v>
+      </c>
+      <c r="J8" s="28">
+        <v>29</v>
+      </c>
       <c r="K8" s="28">
         <v>549</v>
       </c>
@@ -9697,9 +9730,15 @@
       <c r="G9" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
+      <c r="H9" s="28">
+        <v>13</v>
+      </c>
+      <c r="I9" s="28">
+        <v>12.47</v>
+      </c>
+      <c r="J9" s="28">
+        <v>6</v>
+      </c>
       <c r="K9" s="28">
         <v>699</v>
       </c>
@@ -9726,9 +9765,15 @@
       <c r="G10" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
+      <c r="H10" s="28">
+        <v>13</v>
+      </c>
+      <c r="I10" s="28">
+        <v>12.25</v>
+      </c>
+      <c r="J10" s="28">
+        <v>24</v>
+      </c>
       <c r="K10" s="28">
         <v>699</v>
       </c>
@@ -9755,9 +9800,15 @@
       <c r="G11" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="33"/>
+      <c r="H11" s="28">
+        <v>12.57</v>
+      </c>
+      <c r="I11" s="28">
+        <v>12.27</v>
+      </c>
+      <c r="J11" s="28">
+        <v>18</v>
+      </c>
       <c r="K11" s="28">
         <v>699</v>
       </c>
@@ -9784,9 +9835,15 @@
       <c r="G12" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33"/>
+      <c r="H12" s="28">
+        <v>12.56</v>
+      </c>
+      <c r="I12" s="28">
+        <v>12.27</v>
+      </c>
+      <c r="J12" s="28">
+        <v>19</v>
+      </c>
       <c r="K12" s="28">
         <v>698</v>
       </c>
@@ -9813,9 +9870,15 @@
       <c r="G13" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="33"/>
+      <c r="H13" s="28">
+        <v>12</v>
+      </c>
+      <c r="I13" s="28">
+        <v>10.34</v>
+      </c>
+      <c r="J13" s="28">
+        <v>57</v>
+      </c>
       <c r="K13" s="28">
         <v>699</v>
       </c>
@@ -9842,9 +9905,15 @@
       <c r="G14" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="33"/>
+      <c r="H14" s="28">
+        <v>12.54</v>
+      </c>
+      <c r="I14" s="28">
+        <v>12.26</v>
+      </c>
+      <c r="J14" s="28">
+        <v>24</v>
+      </c>
       <c r="K14" s="28">
         <v>697</v>
       </c>
@@ -9871,9 +9940,15 @@
       <c r="G15" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
+      <c r="H15" s="28">
+        <v>12.27</v>
+      </c>
+      <c r="I15" s="28">
+        <v>11.25</v>
+      </c>
+      <c r="J15" s="28">
+        <v>28</v>
+      </c>
       <c r="K15" s="28">
         <v>699</v>
       </c>
@@ -9900,9 +9975,15 @@
       <c r="G16" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="33"/>
+      <c r="H16" s="28">
+        <v>12.53</v>
+      </c>
+      <c r="I16" s="28">
+        <v>12.12</v>
+      </c>
+      <c r="J16" s="28">
+        <v>32</v>
+      </c>
       <c r="K16" s="28">
         <v>698</v>
       </c>
@@ -9929,9 +10010,15 @@
       <c r="G17" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H17" s="33"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="33"/>
+      <c r="H17" s="28">
+        <v>13</v>
+      </c>
+      <c r="I17" s="28">
+        <v>12.18</v>
+      </c>
+      <c r="J17" s="28">
+        <v>32</v>
+      </c>
       <c r="K17" s="28">
         <v>699</v>
       </c>
@@ -9958,9 +10045,15 @@
       <c r="G18" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H18" s="33"/>
-      <c r="I18" s="33"/>
-      <c r="J18" s="33"/>
+      <c r="H18" s="28">
+        <v>12.58</v>
+      </c>
+      <c r="I18" s="28">
+        <v>12.05</v>
+      </c>
+      <c r="J18" s="28">
+        <v>28</v>
+      </c>
       <c r="K18" s="28">
         <v>699</v>
       </c>
@@ -9987,9 +10080,15 @@
       <c r="G19" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H19" s="33"/>
-      <c r="I19" s="33"/>
-      <c r="J19" s="33"/>
+      <c r="H19" s="28">
+        <v>13</v>
+      </c>
+      <c r="I19" s="28">
+        <v>12.17</v>
+      </c>
+      <c r="J19" s="28">
+        <v>30</v>
+      </c>
       <c r="K19" s="28">
         <v>699</v>
       </c>
@@ -10016,9 +10115,15 @@
       <c r="G20" t="s" s="25">
         <v>17</v>
       </c>
-      <c r="H20" s="33"/>
-      <c r="I20" s="33"/>
-      <c r="J20" s="33"/>
+      <c r="H20" s="28">
+        <v>13</v>
+      </c>
+      <c r="I20" s="28">
+        <v>12.02</v>
+      </c>
+      <c r="J20" s="28">
+        <v>35</v>
+      </c>
       <c r="K20" s="28">
         <v>610</v>
       </c>
@@ -10045,9 +10150,15 @@
       <c r="G21" t="s" s="25">
         <v>17</v>
       </c>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="33"/>
+      <c r="H21" s="28">
+        <v>12.53</v>
+      </c>
+      <c r="I21" s="28">
+        <v>11.46</v>
+      </c>
+      <c r="J21" s="28">
+        <v>46</v>
+      </c>
       <c r="K21" s="28">
         <v>604</v>
       </c>
@@ -10074,9 +10185,15 @@
       <c r="G22" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H22" s="33"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
+      <c r="H22" s="28">
+        <v>13</v>
+      </c>
+      <c r="I22" s="28">
+        <v>12.39</v>
+      </c>
+      <c r="J22" s="28">
+        <v>13</v>
+      </c>
       <c r="K22" s="28">
         <v>542</v>
       </c>
@@ -10103,9 +10220,15 @@
       <c r="G23" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H23" s="33"/>
-      <c r="I23" s="33"/>
-      <c r="J23" s="33"/>
+      <c r="H23" s="28">
+        <v>12.51</v>
+      </c>
+      <c r="I23" s="28">
+        <v>12.37</v>
+      </c>
+      <c r="J23" s="28">
+        <v>7</v>
+      </c>
       <c r="K23" s="28">
         <v>549</v>
       </c>
@@ -10132,9 +10255,15 @@
       <c r="G24" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H24" s="33"/>
-      <c r="I24" s="33"/>
-      <c r="J24" s="33"/>
+      <c r="H24" s="28">
+        <v>5.16</v>
+      </c>
+      <c r="I24" s="28">
+        <v>3.44</v>
+      </c>
+      <c r="J24" s="28">
+        <v>11</v>
+      </c>
       <c r="K24" s="28">
         <v>546</v>
       </c>
@@ -10161,9 +10290,15 @@
       <c r="G25" t="s" s="25">
         <v>8</v>
       </c>
-      <c r="H25" s="33"/>
-      <c r="I25" s="33"/>
-      <c r="J25" s="33"/>
+      <c r="H25" s="28">
+        <v>12.54</v>
+      </c>
+      <c r="I25" s="28">
+        <v>12.19</v>
+      </c>
+      <c r="J25" s="28">
+        <v>21</v>
+      </c>
       <c r="K25" s="28">
         <v>698</v>
       </c>
@@ -10190,9 +10325,15 @@
       <c r="G26" t="s" s="25">
         <v>17</v>
       </c>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
+      <c r="H26" s="28">
+        <v>12.51</v>
+      </c>
+      <c r="I26" s="28">
+        <v>11.21</v>
+      </c>
+      <c r="J26" s="28">
+        <v>46</v>
+      </c>
       <c r="K26" s="28">
         <v>699</v>
       </c>
@@ -10219,9 +10360,15 @@
       <c r="G27" t="s" s="25">
         <v>17</v>
       </c>
-      <c r="H27" s="33"/>
-      <c r="I27" s="33"/>
-      <c r="J27" s="33"/>
+      <c r="H27" s="28">
+        <v>12.47</v>
+      </c>
+      <c r="I27" s="28">
+        <v>10.56</v>
+      </c>
+      <c r="J27" s="28">
+        <v>67</v>
+      </c>
       <c r="K27" s="28">
         <v>699</v>
       </c>
@@ -10248,9 +10395,15 @@
       <c r="G28" t="s" s="25">
         <v>252</v>
       </c>
-      <c r="H28" s="33"/>
-      <c r="I28" s="33"/>
-      <c r="J28" s="33"/>
+      <c r="H28" s="28">
+        <v>12.51</v>
+      </c>
+      <c r="I28" s="28">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="J28" s="28">
+        <v>141</v>
+      </c>
       <c r="K28" s="28">
         <v>698</v>
       </c>
@@ -10277,9 +10430,15 @@
       <c r="G29" t="s" s="25">
         <v>17</v>
       </c>
-      <c r="H29" s="33"/>
-      <c r="I29" s="33"/>
-      <c r="J29" s="33"/>
+      <c r="H29" s="28">
+        <v>12.59</v>
+      </c>
+      <c r="I29" s="28">
+        <v>10.12</v>
+      </c>
+      <c r="J29" s="28">
+        <v>86</v>
+      </c>
       <c r="K29" s="28">
         <v>699</v>
       </c>
@@ -10306,9 +10465,15 @@
       <c r="G30" t="s" s="25">
         <v>17</v>
       </c>
-      <c r="H30" s="33"/>
-      <c r="I30" s="33"/>
-      <c r="J30" s="33"/>
+      <c r="H30" s="28">
+        <v>12.52</v>
+      </c>
+      <c r="I30" s="28">
+        <v>10.42</v>
+      </c>
+      <c r="J30" s="28">
+        <v>74</v>
+      </c>
       <c r="K30" s="28">
         <v>699</v>
       </c>

--- a/WjEff.xlsx
+++ b/WjEff.xlsx
@@ -62,7 +62,7 @@
     <t>BETA</t>
   </si>
   <si>
-    <t xml:space="preserve">FLUTE </t>
+    <t xml:space="preserve">SUNSHINE </t>
   </si>
   <si>
     <t>SUNSHINE</t>

--- a/WjEff.xlsx
+++ b/WjEff.xlsx
@@ -877,7 +877,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -915,9 +915,6 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -2126,10 +2123,16 @@
       <c r="G3" t="s" s="9">
         <v>8</v>
       </c>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="14">
+      <c r="H3" s="13">
+        <v>13</v>
+      </c>
+      <c r="I3" s="13">
+        <v>12.31</v>
+      </c>
+      <c r="J3" s="13">
+        <v>18</v>
+      </c>
+      <c r="K3" s="13">
         <v>547</v>
       </c>
     </row>
@@ -2155,10 +2158,16 @@
       <c r="G4" t="s" s="9">
         <v>8</v>
       </c>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="14">
+      <c r="H4" s="13">
+        <v>13</v>
+      </c>
+      <c r="I4" s="13">
+        <v>12.58</v>
+      </c>
+      <c r="J4" s="13">
+        <v>5</v>
+      </c>
+      <c r="K4" s="13">
         <v>547</v>
       </c>
     </row>
@@ -2184,10 +2193,16 @@
       <c r="G5" t="s" s="9">
         <v>8</v>
       </c>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="14">
+      <c r="H5" s="13">
+        <v>13</v>
+      </c>
+      <c r="I5" s="13">
+        <v>12.51</v>
+      </c>
+      <c r="J5" s="13">
+        <v>9</v>
+      </c>
+      <c r="K5" s="13">
         <v>544</v>
       </c>
     </row>
@@ -2213,10 +2228,16 @@
       <c r="G6" t="s" s="9">
         <v>9</v>
       </c>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="14">
+      <c r="H6" s="13">
+        <v>12.49</v>
+      </c>
+      <c r="I6" s="13">
+        <v>12.09</v>
+      </c>
+      <c r="J6" s="13">
+        <v>27</v>
+      </c>
+      <c r="K6" s="13">
         <v>545</v>
       </c>
     </row>
@@ -2240,12 +2261,18 @@
         <v>545</v>
       </c>
       <c r="G7" t="s" s="9">
-        <v>10</v>
-      </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="14">
+        <v>11</v>
+      </c>
+      <c r="H7" s="13">
+        <v>5.08</v>
+      </c>
+      <c r="I7" s="13">
+        <v>2.43</v>
+      </c>
+      <c r="J7" s="13">
+        <v>54</v>
+      </c>
+      <c r="K7" s="13">
         <v>546</v>
       </c>
     </row>
@@ -2271,10 +2298,16 @@
       <c r="G8" t="s" s="9">
         <v>9</v>
       </c>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="14">
+      <c r="H8" s="13">
+        <v>13</v>
+      </c>
+      <c r="I8" s="13">
+        <v>11.54</v>
+      </c>
+      <c r="J8" s="13">
+        <v>29</v>
+      </c>
+      <c r="K8" s="13">
         <v>549</v>
       </c>
     </row>
@@ -2300,10 +2333,16 @@
       <c r="G9" t="s" s="9">
         <v>8</v>
       </c>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="14">
+      <c r="H9" s="13">
+        <v>13</v>
+      </c>
+      <c r="I9" s="13">
+        <v>12.41</v>
+      </c>
+      <c r="J9" s="13">
+        <v>11</v>
+      </c>
+      <c r="K9" s="13">
         <v>699</v>
       </c>
     </row>
@@ -2329,10 +2368,16 @@
       <c r="G10" t="s" s="9">
         <v>8</v>
       </c>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="14">
+      <c r="H10" s="13">
+        <v>12.54</v>
+      </c>
+      <c r="I10" s="13">
+        <v>12.36</v>
+      </c>
+      <c r="J10" s="13">
+        <v>13</v>
+      </c>
+      <c r="K10" s="13">
         <v>699</v>
       </c>
     </row>
@@ -2358,10 +2403,16 @@
       <c r="G11" t="s" s="9">
         <v>8</v>
       </c>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="14">
+      <c r="H11" s="13">
+        <v>12.44</v>
+      </c>
+      <c r="I11" s="13">
+        <v>12.15</v>
+      </c>
+      <c r="J11" s="13">
+        <v>17</v>
+      </c>
+      <c r="K11" s="13">
         <v>699</v>
       </c>
     </row>
@@ -2387,10 +2438,16 @@
       <c r="G12" t="s" s="9">
         <v>8</v>
       </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="14">
+      <c r="H12" s="13">
+        <v>12.42</v>
+      </c>
+      <c r="I12" s="13">
+        <v>12.28</v>
+      </c>
+      <c r="J12" s="13">
+        <v>10</v>
+      </c>
+      <c r="K12" s="13">
         <v>698</v>
       </c>
     </row>
@@ -2416,10 +2473,16 @@
       <c r="G13" t="s" s="9">
         <v>8</v>
       </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="14">
+      <c r="H13" s="13">
+        <v>13</v>
+      </c>
+      <c r="I13" s="13">
+        <v>12.29</v>
+      </c>
+      <c r="J13" s="13">
+        <v>18</v>
+      </c>
+      <c r="K13" s="13">
         <v>699</v>
       </c>
     </row>
@@ -2445,10 +2508,16 @@
       <c r="G14" t="s" s="9">
         <v>8</v>
       </c>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="14">
+      <c r="H14" s="13">
+        <v>12.35</v>
+      </c>
+      <c r="I14" s="13">
+        <v>11.36</v>
+      </c>
+      <c r="J14" s="13">
+        <v>38</v>
+      </c>
+      <c r="K14" s="13">
         <v>697</v>
       </c>
     </row>
@@ -2474,10 +2543,16 @@
       <c r="G15" t="s" s="9">
         <v>8</v>
       </c>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="14">
+      <c r="H15" s="13">
+        <v>12.49</v>
+      </c>
+      <c r="I15" s="13">
+        <v>12.22</v>
+      </c>
+      <c r="J15" s="13">
+        <v>13</v>
+      </c>
+      <c r="K15" s="13">
         <v>699</v>
       </c>
     </row>
@@ -2503,10 +2578,16 @@
       <c r="G16" t="s" s="9">
         <v>8</v>
       </c>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="14">
+      <c r="H16" s="13">
+        <v>12.54</v>
+      </c>
+      <c r="I16" s="13">
+        <v>12.28</v>
+      </c>
+      <c r="J16" s="13">
+        <v>17</v>
+      </c>
+      <c r="K16" s="13">
         <v>698</v>
       </c>
     </row>
@@ -2532,10 +2613,16 @@
       <c r="G17" t="s" s="9">
         <v>8</v>
       </c>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="14">
+      <c r="H17" s="13">
+        <v>12.54</v>
+      </c>
+      <c r="I17" s="13">
+        <v>12.08</v>
+      </c>
+      <c r="J17" s="13">
+        <v>38</v>
+      </c>
+      <c r="K17" s="13">
         <v>699</v>
       </c>
     </row>
@@ -2561,10 +2648,16 @@
       <c r="G18" t="s" s="9">
         <v>8</v>
       </c>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="14">
+      <c r="H18" s="13">
+        <v>12.56</v>
+      </c>
+      <c r="I18" s="13">
+        <v>11.54</v>
+      </c>
+      <c r="J18" s="13">
+        <v>55</v>
+      </c>
+      <c r="K18" s="13">
         <v>699</v>
       </c>
     </row>
@@ -2590,10 +2683,16 @@
       <c r="G19" t="s" s="9">
         <v>8</v>
       </c>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="14">
+      <c r="H19" s="13">
+        <v>12.48</v>
+      </c>
+      <c r="I19" s="13">
+        <v>12.28</v>
+      </c>
+      <c r="J19" s="13">
+        <v>15</v>
+      </c>
+      <c r="K19" s="13">
         <v>699</v>
       </c>
     </row>
@@ -2619,10 +2718,16 @@
       <c r="G20" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="14">
+      <c r="H20" s="13">
+        <v>12.52</v>
+      </c>
+      <c r="I20" s="13">
+        <v>12.14</v>
+      </c>
+      <c r="J20" s="13">
+        <v>19</v>
+      </c>
+      <c r="K20" s="13">
         <v>610</v>
       </c>
     </row>
@@ -2648,10 +2753,16 @@
       <c r="G21" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="14">
+      <c r="H21" s="13">
+        <v>12.58</v>
+      </c>
+      <c r="I21" s="13">
+        <v>12.03</v>
+      </c>
+      <c r="J21" s="13">
+        <v>35</v>
+      </c>
+      <c r="K21" s="13">
         <v>604</v>
       </c>
     </row>
@@ -2677,10 +2788,16 @@
       <c r="G22" t="s" s="9">
         <v>8</v>
       </c>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="14">
+      <c r="H22" s="13">
+        <v>12.55</v>
+      </c>
+      <c r="I22" s="13">
+        <v>12.36</v>
+      </c>
+      <c r="J22" s="13">
+        <v>11</v>
+      </c>
+      <c r="K22" s="13">
         <v>542</v>
       </c>
     </row>
@@ -2706,10 +2823,16 @@
       <c r="G23" t="s" s="9">
         <v>8</v>
       </c>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="14">
+      <c r="H23" s="13">
+        <v>13</v>
+      </c>
+      <c r="I23" s="13">
+        <v>12.52</v>
+      </c>
+      <c r="J23" s="13">
+        <v>7</v>
+      </c>
+      <c r="K23" s="13">
         <v>549</v>
       </c>
     </row>
@@ -2735,10 +2858,16 @@
       <c r="G24" t="s" s="9">
         <v>9</v>
       </c>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="14">
+      <c r="H24" s="13">
+        <v>12.5</v>
+      </c>
+      <c r="I24" s="13">
+        <v>11.31</v>
+      </c>
+      <c r="J24" s="13">
+        <v>40</v>
+      </c>
+      <c r="K24" s="13">
         <v>546</v>
       </c>
     </row>
@@ -2764,10 +2893,16 @@
       <c r="G25" t="s" s="9">
         <v>8</v>
       </c>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="14">
+      <c r="H25" s="13">
+        <v>12.58</v>
+      </c>
+      <c r="I25" s="13">
+        <v>12.28</v>
+      </c>
+      <c r="J25" s="13">
+        <v>21</v>
+      </c>
+      <c r="K25" s="13">
         <v>698</v>
       </c>
     </row>
@@ -2793,10 +2928,16 @@
       <c r="G26" t="s" s="9">
         <v>11</v>
       </c>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="14">
+      <c r="H26" s="13">
+        <v>12.04</v>
+      </c>
+      <c r="I26" s="13">
+        <v>7.09</v>
+      </c>
+      <c r="J26" s="13">
+        <v>127</v>
+      </c>
+      <c r="K26" s="13">
         <v>699</v>
       </c>
     </row>
@@ -2822,10 +2963,16 @@
       <c r="G27" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="14">
+      <c r="H27" s="13">
+        <v>12.16</v>
+      </c>
+      <c r="I27" s="13">
+        <v>11.31</v>
+      </c>
+      <c r="J27" s="13">
+        <v>41</v>
+      </c>
+      <c r="K27" s="13">
         <v>699</v>
       </c>
     </row>
@@ -2851,10 +2998,16 @@
       <c r="G28" t="s" s="9">
         <v>11</v>
       </c>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="14">
+      <c r="H28" s="13">
+        <v>13</v>
+      </c>
+      <c r="I28" s="13">
+        <v>9.25</v>
+      </c>
+      <c r="J28" s="13">
+        <v>171</v>
+      </c>
+      <c r="K28" s="13">
         <v>698</v>
       </c>
     </row>
@@ -2880,10 +3033,16 @@
       <c r="G29" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="14">
+      <c r="H29" s="13">
+        <v>12.5</v>
+      </c>
+      <c r="I29" s="13">
+        <v>11.34</v>
+      </c>
+      <c r="J29" s="13">
+        <v>47</v>
+      </c>
+      <c r="K29" s="13">
         <v>699</v>
       </c>
     </row>
@@ -2907,12 +3066,18 @@
         <v>699</v>
       </c>
       <c r="G30" t="s" s="9">
-        <v>10</v>
-      </c>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="14">
+        <v>11</v>
+      </c>
+      <c r="H30" s="13">
+        <v>9.5</v>
+      </c>
+      <c r="I30" s="13">
+        <v>7.27</v>
+      </c>
+      <c r="J30" s="13">
+        <v>84</v>
+      </c>
+      <c r="K30" s="13">
         <v>699</v>
       </c>
     </row>
@@ -2934,16 +3099,16 @@
   <dimension ref="A1:K30"/>
   <sheetFormatPr defaultColWidth="9.16667" defaultRowHeight="15.4" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9.17188" style="24" customWidth="1"/>
-    <col min="2" max="2" width="11" style="24" customWidth="1"/>
-    <col min="3" max="6" width="9.17188" style="24" customWidth="1"/>
-    <col min="7" max="7" width="9.85156" style="24" customWidth="1"/>
-    <col min="8" max="11" width="9.17188" style="24" customWidth="1"/>
-    <col min="12" max="16384" width="9.17188" style="24" customWidth="1"/>
+    <col min="1" max="1" width="9.17188" style="23" customWidth="1"/>
+    <col min="2" max="2" width="11" style="23" customWidth="1"/>
+    <col min="3" max="6" width="9.17188" style="23" customWidth="1"/>
+    <col min="7" max="7" width="9.85156" style="23" customWidth="1"/>
+    <col min="8" max="11" width="9.17188" style="23" customWidth="1"/>
+    <col min="12" max="16384" width="9.17188" style="23" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="23"/>
+      <c r="A1" s="22"/>
       <c r="B1" t="s" s="3">
         <v>0</v>
       </c>
@@ -3992,16 +4157,16 @@
   <dimension ref="A1:K30"/>
   <sheetFormatPr defaultColWidth="9.16667" defaultRowHeight="15.4" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9.17188" style="25" customWidth="1"/>
-    <col min="2" max="2" width="11" style="25" customWidth="1"/>
-    <col min="3" max="6" width="9.17188" style="25" customWidth="1"/>
-    <col min="7" max="7" width="9.85156" style="25" customWidth="1"/>
-    <col min="8" max="11" width="9.17188" style="25" customWidth="1"/>
-    <col min="12" max="16384" width="9.17188" style="25" customWidth="1"/>
+    <col min="1" max="1" width="9.17188" style="24" customWidth="1"/>
+    <col min="2" max="2" width="11" style="24" customWidth="1"/>
+    <col min="3" max="6" width="9.17188" style="24" customWidth="1"/>
+    <col min="7" max="7" width="9.85156" style="24" customWidth="1"/>
+    <col min="8" max="11" width="9.17188" style="24" customWidth="1"/>
+    <col min="12" max="16384" width="9.17188" style="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="23"/>
+      <c r="A1" s="22"/>
       <c r="B1" t="s" s="3">
         <v>0</v>
       </c>
@@ -5050,16 +5215,16 @@
   <dimension ref="A1:K30"/>
   <sheetFormatPr defaultColWidth="9.16667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9.17188" style="26" customWidth="1"/>
-    <col min="2" max="2" width="11" style="26" customWidth="1"/>
-    <col min="3" max="6" width="9.17188" style="26" customWidth="1"/>
-    <col min="7" max="7" width="9.85156" style="26" customWidth="1"/>
-    <col min="8" max="11" width="9.17188" style="26" customWidth="1"/>
-    <col min="12" max="16384" width="9.17188" style="26" customWidth="1"/>
+    <col min="1" max="1" width="9.17188" style="25" customWidth="1"/>
+    <col min="2" max="2" width="11" style="25" customWidth="1"/>
+    <col min="3" max="6" width="9.17188" style="25" customWidth="1"/>
+    <col min="7" max="7" width="9.85156" style="25" customWidth="1"/>
+    <col min="8" max="11" width="9.17188" style="25" customWidth="1"/>
+    <col min="12" max="16384" width="9.17188" style="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="23"/>
+      <c r="A1" s="22"/>
       <c r="B1" t="s" s="3">
         <v>0</v>
       </c>
@@ -6108,12 +6273,12 @@
   <dimension ref="A1:L30"/>
   <sheetFormatPr defaultColWidth="9.16667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="12" width="9.17188" style="27" customWidth="1"/>
-    <col min="13" max="16384" width="9.17188" style="27" customWidth="1"/>
+    <col min="1" max="12" width="9.17188" style="26" customWidth="1"/>
+    <col min="13" max="16384" width="9.17188" style="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="23"/>
+      <c r="A1" s="22"/>
       <c r="B1" t="s" s="3">
         <v>0</v>
       </c>
@@ -6128,7 +6293,7 @@
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
       <c r="K1" s="4"/>
-      <c r="L1" s="23"/>
+      <c r="L1" s="22"/>
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="s" s="7">
@@ -6164,7 +6329,7 @@
       <c r="K2" t="s" s="7">
         <v>7</v>
       </c>
-      <c r="L2" s="23"/>
+      <c r="L2" s="22"/>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="12">
@@ -6200,7 +6365,7 @@
       <c r="K3" s="12">
         <v>547</v>
       </c>
-      <c r="L3" s="23"/>
+      <c r="L3" s="22"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="12">
@@ -6236,7 +6401,7 @@
       <c r="K4" s="12">
         <v>546</v>
       </c>
-      <c r="L4" s="23"/>
+      <c r="L4" s="22"/>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="12">
@@ -6272,7 +6437,7 @@
       <c r="K5" s="12">
         <v>543</v>
       </c>
-      <c r="L5" s="23"/>
+      <c r="L5" s="22"/>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="12">
@@ -6308,7 +6473,7 @@
       <c r="K6" s="12">
         <v>545</v>
       </c>
-      <c r="L6" s="23"/>
+      <c r="L6" s="22"/>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="12">
@@ -6344,7 +6509,7 @@
       <c r="K7" s="12">
         <v>546</v>
       </c>
-      <c r="L7" s="23"/>
+      <c r="L7" s="22"/>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="12">
@@ -6380,7 +6545,7 @@
       <c r="K8" s="12">
         <v>549</v>
       </c>
-      <c r="L8" s="23"/>
+      <c r="L8" s="22"/>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="12">
@@ -6416,7 +6581,7 @@
       <c r="K9" s="12">
         <v>699</v>
       </c>
-      <c r="L9" s="23"/>
+      <c r="L9" s="22"/>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="12">
@@ -6452,7 +6617,7 @@
       <c r="K10" s="12">
         <v>699</v>
       </c>
-      <c r="L10" s="23"/>
+      <c r="L10" s="22"/>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="12">
@@ -6488,7 +6653,7 @@
       <c r="K11" s="12">
         <v>699</v>
       </c>
-      <c r="L11" s="23"/>
+      <c r="L11" s="22"/>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="12">
@@ -6524,7 +6689,7 @@
       <c r="K12" s="12">
         <v>699</v>
       </c>
-      <c r="L12" s="23"/>
+      <c r="L12" s="22"/>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="12">
@@ -6560,7 +6725,7 @@
       <c r="K13" s="12">
         <v>699</v>
       </c>
-      <c r="L13" s="23"/>
+      <c r="L13" s="22"/>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="12">
@@ -6596,7 +6761,7 @@
       <c r="K14" s="12">
         <v>698</v>
       </c>
-      <c r="L14" s="23"/>
+      <c r="L14" s="22"/>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="12">
@@ -6632,7 +6797,7 @@
       <c r="K15" s="12">
         <v>699</v>
       </c>
-      <c r="L15" s="23"/>
+      <c r="L15" s="22"/>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="12">
@@ -6668,7 +6833,7 @@
       <c r="K16" s="12">
         <v>699</v>
       </c>
-      <c r="L16" s="23"/>
+      <c r="L16" s="22"/>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="12">
@@ -6704,7 +6869,7 @@
       <c r="K17" s="12">
         <v>698</v>
       </c>
-      <c r="L17" s="23"/>
+      <c r="L17" s="22"/>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="12">
@@ -6740,7 +6905,7 @@
       <c r="K18" s="12">
         <v>674</v>
       </c>
-      <c r="L18" s="23"/>
+      <c r="L18" s="22"/>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="12">
@@ -6776,7 +6941,7 @@
       <c r="K19" s="12">
         <v>699</v>
       </c>
-      <c r="L19" s="23"/>
+      <c r="L19" s="22"/>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="12">
@@ -6812,7 +6977,7 @@
       <c r="K20" s="12">
         <v>611</v>
       </c>
-      <c r="L20" s="23"/>
+      <c r="L20" s="22"/>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="12">
@@ -6848,7 +7013,7 @@
       <c r="K21" s="12">
         <v>606</v>
       </c>
-      <c r="L21" s="23"/>
+      <c r="L21" s="22"/>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="12">
@@ -6884,7 +7049,7 @@
       <c r="K22" s="12">
         <v>541</v>
       </c>
-      <c r="L22" s="23"/>
+      <c r="L22" s="22"/>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="12">
@@ -6920,7 +7085,7 @@
       <c r="K23" s="12">
         <v>548</v>
       </c>
-      <c r="L23" s="23"/>
+      <c r="L23" s="22"/>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="12">
@@ -6956,7 +7121,7 @@
       <c r="K24" s="12">
         <v>546</v>
       </c>
-      <c r="L24" s="23"/>
+      <c r="L24" s="22"/>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="12">
@@ -6992,7 +7157,7 @@
       <c r="K25" s="12">
         <v>699</v>
       </c>
-      <c r="L25" s="23"/>
+      <c r="L25" s="22"/>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="12">
@@ -7028,7 +7193,7 @@
       <c r="K26" s="12">
         <v>699</v>
       </c>
-      <c r="L26" s="23"/>
+      <c r="L26" s="22"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="12">
@@ -7064,7 +7229,7 @@
       <c r="K27" s="12">
         <v>699</v>
       </c>
-      <c r="L27" s="23"/>
+      <c r="L27" s="22"/>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="12">
@@ -7100,7 +7265,7 @@
       <c r="K28" s="12">
         <v>699</v>
       </c>
-      <c r="L28" s="23"/>
+      <c r="L28" s="22"/>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="12">
@@ -7136,7 +7301,7 @@
       <c r="K29" s="12">
         <v>698</v>
       </c>
-      <c r="L29" s="23"/>
+      <c r="L29" s="22"/>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="12">
@@ -7172,7 +7337,7 @@
       <c r="K30" s="12">
         <v>699</v>
       </c>
-      <c r="L30" s="23"/>
+      <c r="L30" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7192,12 +7357,12 @@
   <dimension ref="A1:K30"/>
   <sheetFormatPr defaultColWidth="9.16667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="11" width="9.17188" style="28" customWidth="1"/>
-    <col min="12" max="16384" width="9.17188" style="28" customWidth="1"/>
+    <col min="1" max="11" width="9.17188" style="27" customWidth="1"/>
+    <col min="12" max="16384" width="9.17188" style="27" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="23"/>
+      <c r="A1" s="22"/>
       <c r="B1" t="s" s="3">
         <v>0</v>
       </c>
@@ -8246,12 +8411,12 @@
   <dimension ref="A1:K30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="11" width="9" style="29" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="29" customWidth="1"/>
+    <col min="1" max="11" width="9" style="28" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="23"/>
+      <c r="A1" s="22"/>
       <c r="B1" t="s" s="3">
         <v>0</v>
       </c>
@@ -9300,12 +9465,12 @@
   <dimension ref="A1:K30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="11" width="9" style="30" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="30" customWidth="1"/>
+    <col min="1" max="11" width="9" style="29" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="29" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="23"/>
+      <c r="A1" s="22"/>
       <c r="B1" t="s" s="3">
         <v>0</v>
       </c>
@@ -9748,9 +9913,9 @@
       <c r="B14" t="s" s="7">
         <v>12</v>
       </c>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
       <c r="F14" s="12">
         <v>698</v>
       </c>
@@ -10348,12 +10513,12 @@
   <dimension ref="A1:K30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="11" width="9" style="31" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="31" customWidth="1"/>
+    <col min="1" max="11" width="9" style="30" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="23"/>
+      <c r="A1" s="22"/>
       <c r="B1" t="s" s="3">
         <v>0</v>
       </c>
@@ -10793,17 +10958,17 @@
       <c r="A14" s="12">
         <v>12</v>
       </c>
-      <c r="B14" s="23"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
       <c r="F14" s="12">
         <v>698</v>
       </c>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
       <c r="K14" s="12">
         <v>698</v>
       </c>
@@ -11386,14 +11551,14 @@
   <dimension ref="A1:K30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.4" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9" style="32" customWidth="1"/>
-    <col min="2" max="2" width="10.8516" style="32" customWidth="1"/>
-    <col min="3" max="11" width="9" style="32" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="32" customWidth="1"/>
+    <col min="1" max="1" width="9" style="31" customWidth="1"/>
+    <col min="2" max="2" width="10.8516" style="31" customWidth="1"/>
+    <col min="3" max="11" width="9" style="31" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="31" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="23"/>
+      <c r="A1" s="22"/>
       <c r="B1" t="s" s="3">
         <v>0</v>
       </c>
@@ -11848,10 +12013,10 @@
       <c r="F14" s="12">
         <v>698</v>
       </c>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
       <c r="K14" s="12">
         <v>698</v>
       </c>
@@ -12434,36 +12599,36 @@
   <dimension ref="A1:K30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9" style="33" customWidth="1"/>
-    <col min="2" max="2" width="10.8516" style="33" customWidth="1"/>
-    <col min="3" max="3" width="6.67188" style="33" customWidth="1"/>
-    <col min="4" max="4" width="5.5" style="33" customWidth="1"/>
-    <col min="5" max="5" width="5.85156" style="33" customWidth="1"/>
-    <col min="6" max="6" width="7.17188" style="33" customWidth="1"/>
-    <col min="7" max="7" width="9.85156" style="33" customWidth="1"/>
-    <col min="8" max="8" width="6.67188" style="33" customWidth="1"/>
-    <col min="9" max="9" width="5.5" style="33" customWidth="1"/>
-    <col min="10" max="10" width="5.85156" style="33" customWidth="1"/>
-    <col min="11" max="11" width="7.17188" style="33" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="33" customWidth="1"/>
+    <col min="1" max="1" width="9" style="32" customWidth="1"/>
+    <col min="2" max="2" width="10.8516" style="32" customWidth="1"/>
+    <col min="3" max="3" width="6.67188" style="32" customWidth="1"/>
+    <col min="4" max="4" width="5.5" style="32" customWidth="1"/>
+    <col min="5" max="5" width="5.85156" style="32" customWidth="1"/>
+    <col min="6" max="6" width="7.17188" style="32" customWidth="1"/>
+    <col min="7" max="7" width="9.85156" style="32" customWidth="1"/>
+    <col min="8" max="8" width="6.67188" style="32" customWidth="1"/>
+    <col min="9" max="9" width="5.5" style="32" customWidth="1"/>
+    <col min="10" max="10" width="5.85156" style="32" customWidth="1"/>
+    <col min="11" max="11" width="7.17188" style="32" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="32" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="23"/>
+      <c r="A1" s="22"/>
       <c r="B1" t="s" s="3">
         <v>0</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
-      <c r="F1" s="34"/>
+      <c r="F1" s="33"/>
       <c r="G1" t="s" s="3">
         <v>1</v>
       </c>
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
-      <c r="K1" s="34"/>
+      <c r="K1" s="33"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" t="s" s="7">
@@ -12481,7 +12646,7 @@
       <c r="E2" t="s" s="7">
         <v>6</v>
       </c>
-      <c r="F2" t="s" s="35">
+      <c r="F2" t="s" s="34">
         <v>7</v>
       </c>
       <c r="G2" t="s" s="7">
@@ -12496,7 +12661,7 @@
       <c r="J2" t="s" s="7">
         <v>6</v>
       </c>
-      <c r="K2" t="s" s="35">
+      <c r="K2" t="s" s="34">
         <v>7</v>
       </c>
     </row>
@@ -12516,7 +12681,7 @@
       <c r="E3" s="12">
         <v>20</v>
       </c>
-      <c r="F3" s="36">
+      <c r="F3" s="35">
         <v>547</v>
       </c>
       <c r="G3" t="s" s="7">
@@ -12531,7 +12696,7 @@
       <c r="J3" s="12">
         <v>12</v>
       </c>
-      <c r="K3" s="36">
+      <c r="K3" s="35">
         <v>547</v>
       </c>
     </row>
@@ -12551,7 +12716,7 @@
       <c r="E4" s="12">
         <v>29</v>
       </c>
-      <c r="F4" s="36">
+      <c r="F4" s="35">
         <v>546</v>
       </c>
       <c r="G4" t="s" s="7">
@@ -12566,7 +12731,7 @@
       <c r="J4" s="12">
         <v>25</v>
       </c>
-      <c r="K4" s="36">
+      <c r="K4" s="35">
         <v>546</v>
       </c>
     </row>
@@ -12586,7 +12751,7 @@
       <c r="E5" s="12">
         <v>30</v>
       </c>
-      <c r="F5" s="36">
+      <c r="F5" s="35">
         <v>543</v>
       </c>
       <c r="G5" t="s" s="7">
@@ -12601,7 +12766,7 @@
       <c r="J5" s="12">
         <v>30</v>
       </c>
-      <c r="K5" s="36">
+      <c r="K5" s="35">
         <v>543</v>
       </c>
     </row>
@@ -12621,7 +12786,7 @@
       <c r="E6" s="12">
         <v>41</v>
       </c>
-      <c r="F6" s="36">
+      <c r="F6" s="35">
         <v>545</v>
       </c>
       <c r="G6" t="s" s="7">
@@ -12636,7 +12801,7 @@
       <c r="J6" s="12">
         <v>43</v>
       </c>
-      <c r="K6" s="36">
+      <c r="K6" s="35">
         <v>545</v>
       </c>
     </row>
@@ -12656,7 +12821,7 @@
       <c r="E7" s="12">
         <v>20</v>
       </c>
-      <c r="F7" s="36">
+      <c r="F7" s="35">
         <v>546</v>
       </c>
       <c r="G7" t="s" s="7">
@@ -12671,7 +12836,7 @@
       <c r="J7" s="12">
         <v>23</v>
       </c>
-      <c r="K7" s="36">
+      <c r="K7" s="35">
         <v>546</v>
       </c>
     </row>
@@ -12691,7 +12856,7 @@
       <c r="E8" s="12">
         <v>14</v>
       </c>
-      <c r="F8" s="36">
+      <c r="F8" s="35">
         <v>549</v>
       </c>
       <c r="G8" t="s" s="7">
@@ -12706,7 +12871,7 @@
       <c r="J8" s="12">
         <v>17</v>
       </c>
-      <c r="K8" s="36">
+      <c r="K8" s="35">
         <v>549</v>
       </c>
     </row>
@@ -12726,7 +12891,7 @@
       <c r="E9" s="12">
         <v>10</v>
       </c>
-      <c r="F9" s="36">
+      <c r="F9" s="35">
         <v>699</v>
       </c>
       <c r="G9" t="s" s="7">
@@ -12741,7 +12906,7 @@
       <c r="J9" s="12">
         <v>19</v>
       </c>
-      <c r="K9" s="36">
+      <c r="K9" s="35">
         <v>699</v>
       </c>
     </row>
@@ -12761,7 +12926,7 @@
       <c r="E10" s="12">
         <v>21</v>
       </c>
-      <c r="F10" s="36">
+      <c r="F10" s="35">
         <v>699</v>
       </c>
       <c r="G10" t="s" s="7">
@@ -12776,7 +12941,7 @@
       <c r="J10" s="12">
         <v>23</v>
       </c>
-      <c r="K10" s="36">
+      <c r="K10" s="35">
         <v>699</v>
       </c>
     </row>
@@ -12796,7 +12961,7 @@
       <c r="E11" s="12">
         <v>29</v>
       </c>
-      <c r="F11" s="36">
+      <c r="F11" s="35">
         <v>699</v>
       </c>
       <c r="G11" t="s" s="7">
@@ -12811,7 +12976,7 @@
       <c r="J11" s="12">
         <v>21</v>
       </c>
-      <c r="K11" s="36">
+      <c r="K11" s="35">
         <v>699</v>
       </c>
     </row>
@@ -12831,7 +12996,7 @@
       <c r="E12" s="12">
         <v>15</v>
       </c>
-      <c r="F12" s="36">
+      <c r="F12" s="35">
         <v>699</v>
       </c>
       <c r="G12" t="s" s="7">
@@ -12846,7 +13011,7 @@
       <c r="J12" s="12">
         <v>26</v>
       </c>
-      <c r="K12" s="36">
+      <c r="K12" s="35">
         <v>699</v>
       </c>
     </row>
@@ -12866,7 +13031,7 @@
       <c r="E13" s="12">
         <v>25</v>
       </c>
-      <c r="F13" s="36">
+      <c r="F13" s="35">
         <v>699</v>
       </c>
       <c r="G13" t="s" s="7">
@@ -12881,7 +13046,7 @@
       <c r="J13" s="12">
         <v>19</v>
       </c>
-      <c r="K13" s="36">
+      <c r="K13" s="35">
         <v>699</v>
       </c>
     </row>
@@ -12901,7 +13066,7 @@
       <c r="E14" s="12">
         <v>45</v>
       </c>
-      <c r="F14" s="36">
+      <c r="F14" s="35">
         <v>698</v>
       </c>
       <c r="G14" t="s" s="7">
@@ -12916,7 +13081,7 @@
       <c r="J14" s="12">
         <v>46</v>
       </c>
-      <c r="K14" s="36">
+      <c r="K14" s="35">
         <v>698</v>
       </c>
     </row>
@@ -12936,7 +13101,7 @@
       <c r="E15" s="12">
         <v>31</v>
       </c>
-      <c r="F15" s="36">
+      <c r="F15" s="35">
         <v>699</v>
       </c>
       <c r="G15" t="s" s="7">
@@ -12951,7 +13116,7 @@
       <c r="J15" s="12">
         <v>70</v>
       </c>
-      <c r="K15" s="36">
+      <c r="K15" s="35">
         <v>699</v>
       </c>
     </row>
@@ -12971,7 +13136,7 @@
       <c r="E16" s="12">
         <v>18</v>
       </c>
-      <c r="F16" s="36">
+      <c r="F16" s="35">
         <v>699</v>
       </c>
       <c r="G16" t="s" s="7">
@@ -12986,7 +13151,7 @@
       <c r="J16" s="12">
         <v>18</v>
       </c>
-      <c r="K16" s="36">
+      <c r="K16" s="35">
         <v>699</v>
       </c>
     </row>
@@ -13006,7 +13171,7 @@
       <c r="E17" s="12">
         <v>31</v>
       </c>
-      <c r="F17" s="36">
+      <c r="F17" s="35">
         <v>698</v>
       </c>
       <c r="G17" t="s" s="7">
@@ -13021,7 +13186,7 @@
       <c r="J17" s="12">
         <v>38</v>
       </c>
-      <c r="K17" s="36">
+      <c r="K17" s="35">
         <v>698</v>
       </c>
     </row>
@@ -13041,7 +13206,7 @@
       <c r="E18" s="12">
         <v>31</v>
       </c>
-      <c r="F18" s="36">
+      <c r="F18" s="35">
         <v>674</v>
       </c>
       <c r="G18" t="s" s="7">
@@ -13056,7 +13221,7 @@
       <c r="J18" s="12">
         <v>64</v>
       </c>
-      <c r="K18" s="36">
+      <c r="K18" s="35">
         <v>674</v>
       </c>
     </row>
@@ -13076,7 +13241,7 @@
       <c r="E19" s="12">
         <v>24</v>
       </c>
-      <c r="F19" s="36">
+      <c r="F19" s="35">
         <v>699</v>
       </c>
       <c r="G19" t="s" s="7">
@@ -13091,7 +13256,7 @@
       <c r="J19" s="12">
         <v>20</v>
       </c>
-      <c r="K19" s="36">
+      <c r="K19" s="35">
         <v>699</v>
       </c>
     </row>
@@ -13111,7 +13276,7 @@
       <c r="E20" s="12">
         <v>46</v>
       </c>
-      <c r="F20" s="36">
+      <c r="F20" s="35">
         <v>611</v>
       </c>
       <c r="G20" t="s" s="7">
@@ -13126,7 +13291,7 @@
       <c r="J20" s="12">
         <v>39</v>
       </c>
-      <c r="K20" s="36">
+      <c r="K20" s="35">
         <v>611</v>
       </c>
     </row>
@@ -13146,7 +13311,7 @@
       <c r="E21" s="12">
         <v>35</v>
       </c>
-      <c r="F21" s="36">
+      <c r="F21" s="35">
         <v>606</v>
       </c>
       <c r="G21" t="s" s="7">
@@ -13161,7 +13326,7 @@
       <c r="J21" s="12">
         <v>22</v>
       </c>
-      <c r="K21" s="36">
+      <c r="K21" s="35">
         <v>606</v>
       </c>
     </row>
@@ -13181,7 +13346,7 @@
       <c r="E22" s="12">
         <v>37</v>
       </c>
-      <c r="F22" s="36">
+      <c r="F22" s="35">
         <v>541</v>
       </c>
       <c r="G22" t="s" s="7">
@@ -13196,7 +13361,7 @@
       <c r="J22" s="12">
         <v>24</v>
       </c>
-      <c r="K22" s="36">
+      <c r="K22" s="35">
         <v>541</v>
       </c>
     </row>
@@ -13216,7 +13381,7 @@
       <c r="E23" s="12">
         <v>14</v>
       </c>
-      <c r="F23" s="36">
+      <c r="F23" s="35">
         <v>548</v>
       </c>
       <c r="G23" t="s" s="7">
@@ -13231,7 +13396,7 @@
       <c r="J23" s="12">
         <v>16</v>
       </c>
-      <c r="K23" s="36">
+      <c r="K23" s="35">
         <v>548</v>
       </c>
     </row>
@@ -13251,7 +13416,7 @@
       <c r="E24" s="12">
         <v>11</v>
       </c>
-      <c r="F24" s="36">
+      <c r="F24" s="35">
         <v>546</v>
       </c>
       <c r="G24" t="s" s="7">
@@ -13266,7 +13431,7 @@
       <c r="J24" s="12">
         <v>12</v>
       </c>
-      <c r="K24" s="36">
+      <c r="K24" s="35">
         <v>546</v>
       </c>
     </row>
@@ -13286,7 +13451,7 @@
       <c r="E25" s="12">
         <v>31</v>
       </c>
-      <c r="F25" s="36">
+      <c r="F25" s="35">
         <v>699</v>
       </c>
       <c r="G25" t="s" s="7">
@@ -13301,7 +13466,7 @@
       <c r="J25" s="12">
         <v>24</v>
       </c>
-      <c r="K25" s="36">
+      <c r="K25" s="35">
         <v>699</v>
       </c>
     </row>
@@ -13321,7 +13486,7 @@
       <c r="E26" s="12">
         <v>34</v>
       </c>
-      <c r="F26" s="36">
+      <c r="F26" s="35">
         <v>699</v>
       </c>
       <c r="G26" t="s" s="7">
@@ -13336,7 +13501,7 @@
       <c r="J26" s="12">
         <v>31</v>
       </c>
-      <c r="K26" s="36">
+      <c r="K26" s="35">
         <v>699</v>
       </c>
     </row>
@@ -13356,7 +13521,7 @@
       <c r="E27" s="12">
         <v>46</v>
       </c>
-      <c r="F27" s="36">
+      <c r="F27" s="35">
         <v>699</v>
       </c>
       <c r="G27" t="s" s="7">
@@ -13371,7 +13536,7 @@
       <c r="J27" s="12">
         <v>48</v>
       </c>
-      <c r="K27" s="36">
+      <c r="K27" s="35">
         <v>699</v>
       </c>
     </row>
@@ -13391,7 +13556,7 @@
       <c r="E28" s="12">
         <v>33</v>
       </c>
-      <c r="F28" s="36">
+      <c r="F28" s="35">
         <v>699</v>
       </c>
       <c r="G28" t="s" s="7">
@@ -13406,7 +13571,7 @@
       <c r="J28" s="12">
         <v>38</v>
       </c>
-      <c r="K28" s="36">
+      <c r="K28" s="35">
         <v>699</v>
       </c>
     </row>
@@ -13426,7 +13591,7 @@
       <c r="E29" s="12">
         <v>54</v>
       </c>
-      <c r="F29" s="36">
+      <c r="F29" s="35">
         <v>698</v>
       </c>
       <c r="G29" t="s" s="7">
@@ -13441,7 +13606,7 @@
       <c r="J29" s="12">
         <v>36</v>
       </c>
-      <c r="K29" s="36">
+      <c r="K29" s="35">
         <v>698</v>
       </c>
     </row>
@@ -13461,7 +13626,7 @@
       <c r="E30" s="12">
         <v>33</v>
       </c>
-      <c r="F30" s="36">
+      <c r="F30" s="35">
         <v>699</v>
       </c>
       <c r="G30" t="s" s="7">
@@ -13476,7 +13641,7 @@
       <c r="J30" s="12">
         <v>63</v>
       </c>
-      <c r="K30" s="36">
+      <c r="K30" s="35">
         <v>699</v>
       </c>
     </row>
@@ -13498,12 +13663,12 @@
   <dimension ref="A1:K30"/>
   <sheetFormatPr defaultColWidth="9.16667" defaultRowHeight="15.4" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="2.67188" style="15" customWidth="1"/>
-    <col min="2" max="2" width="11" style="15" customWidth="1"/>
-    <col min="3" max="6" width="9.17188" style="15" customWidth="1"/>
-    <col min="7" max="7" width="9.85156" style="15" customWidth="1"/>
-    <col min="8" max="11" width="9.17188" style="15" customWidth="1"/>
-    <col min="12" max="16384" width="9.17188" style="15" customWidth="1"/>
+    <col min="1" max="1" width="2.67188" style="14" customWidth="1"/>
+    <col min="2" max="2" width="11" style="14" customWidth="1"/>
+    <col min="3" max="6" width="9.17188" style="14" customWidth="1"/>
+    <col min="7" max="7" width="9.85156" style="14" customWidth="1"/>
+    <col min="8" max="11" width="9.17188" style="14" customWidth="1"/>
+    <col min="12" max="16384" width="9.17188" style="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -13580,16 +13745,16 @@
       <c r="G3" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H3" s="14">
+      <c r="H3" s="13">
         <v>12.34</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="13">
         <v>11.51</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="13">
         <v>18</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="13">
         <v>547</v>
       </c>
     </row>
@@ -13615,16 +13780,16 @@
       <c r="G4" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="13">
         <v>12.32</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="13">
         <v>12.12</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="13">
         <v>13</v>
       </c>
-      <c r="K4" s="14">
+      <c r="K4" s="13">
         <v>547</v>
       </c>
     </row>
@@ -13650,16 +13815,16 @@
       <c r="G5" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="13">
         <v>12.33</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="13">
         <v>12.21</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="13">
         <v>7</v>
       </c>
-      <c r="K5" s="14">
+      <c r="K5" s="13">
         <v>544</v>
       </c>
     </row>
@@ -13685,16 +13850,16 @@
       <c r="G6" t="s" s="9">
         <v>9</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="13">
         <v>12.25</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="13">
         <v>11.34</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="13">
         <v>34</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="13">
         <v>545</v>
       </c>
     </row>
@@ -13720,16 +13885,16 @@
       <c r="G7" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="13">
         <v>11.56</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="13">
         <v>10.48</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="13">
         <v>30</v>
       </c>
-      <c r="K7" s="14">
+      <c r="K7" s="13">
         <v>546</v>
       </c>
     </row>
@@ -13755,16 +13920,16 @@
       <c r="G8" t="s" s="9">
         <v>9</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="13">
         <v>3.05</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="13">
         <v>2.37</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="13">
         <v>15</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="13">
         <v>549</v>
       </c>
     </row>
@@ -13790,16 +13955,16 @@
       <c r="G9" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="13">
         <v>12.35</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="13">
         <v>12.19</v>
       </c>
-      <c r="J9" s="14">
-        <v>11</v>
-      </c>
-      <c r="K9" s="14">
+      <c r="J9" s="13">
+        <v>11</v>
+      </c>
+      <c r="K9" s="13">
         <v>699</v>
       </c>
     </row>
@@ -13825,16 +13990,16 @@
       <c r="G10" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="13">
         <v>12.15</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="13">
         <v>10.45</v>
       </c>
-      <c r="J10" s="14">
+      <c r="J10" s="13">
         <v>57</v>
       </c>
-      <c r="K10" s="14">
+      <c r="K10" s="13">
         <v>699</v>
       </c>
     </row>
@@ -13860,16 +14025,16 @@
       <c r="G11" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="13">
         <v>12.37</v>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="13">
         <v>11.57</v>
       </c>
-      <c r="J11" s="14">
+      <c r="J11" s="13">
         <v>19</v>
       </c>
-      <c r="K11" s="14">
+      <c r="K11" s="13">
         <v>699</v>
       </c>
     </row>
@@ -13895,16 +14060,16 @@
       <c r="G12" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="13">
         <v>12.24</v>
       </c>
-      <c r="I12" s="14">
+      <c r="I12" s="13">
         <v>12.02</v>
       </c>
-      <c r="J12" s="14">
+      <c r="J12" s="13">
         <v>23</v>
       </c>
-      <c r="K12" s="14">
+      <c r="K12" s="13">
         <v>698</v>
       </c>
     </row>
@@ -13930,16 +14095,16 @@
       <c r="G13" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="13">
         <v>12.24</v>
       </c>
-      <c r="I13" s="14">
+      <c r="I13" s="13">
         <v>11.21</v>
       </c>
-      <c r="J13" s="14">
+      <c r="J13" s="13">
         <v>44</v>
       </c>
-      <c r="K13" s="14">
+      <c r="K13" s="13">
         <v>699</v>
       </c>
     </row>
@@ -13965,16 +14130,16 @@
       <c r="G14" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="13">
         <v>12.28</v>
       </c>
-      <c r="I14" s="14">
+      <c r="I14" s="13">
         <v>12.15</v>
       </c>
-      <c r="J14" s="14">
+      <c r="J14" s="13">
         <v>15</v>
       </c>
-      <c r="K14" s="14">
+      <c r="K14" s="13">
         <v>697</v>
       </c>
     </row>
@@ -14000,16 +14165,16 @@
       <c r="G15" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H15" s="13">
         <v>12.25</v>
       </c>
-      <c r="I15" s="14">
+      <c r="I15" s="13">
         <v>11.44</v>
       </c>
-      <c r="J15" s="14">
+      <c r="J15" s="13">
         <v>26</v>
       </c>
-      <c r="K15" s="14">
+      <c r="K15" s="13">
         <v>699</v>
       </c>
     </row>
@@ -14035,16 +14200,16 @@
       <c r="G16" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="13">
         <v>12.36</v>
       </c>
-      <c r="I16" s="14">
+      <c r="I16" s="13">
         <v>12.22</v>
       </c>
-      <c r="J16" s="14">
+      <c r="J16" s="13">
         <v>16</v>
       </c>
-      <c r="K16" s="14">
+      <c r="K16" s="13">
         <v>698</v>
       </c>
     </row>
@@ -14070,16 +14235,16 @@
       <c r="G17" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H17" s="14">
+      <c r="H17" s="13">
         <v>12.25</v>
       </c>
-      <c r="I17" s="14">
+      <c r="I17" s="13">
         <v>11.36</v>
       </c>
-      <c r="J17" s="14">
+      <c r="J17" s="13">
         <v>31</v>
       </c>
-      <c r="K17" s="14">
+      <c r="K17" s="13">
         <v>699</v>
       </c>
     </row>
@@ -14105,16 +14270,16 @@
       <c r="G18" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H18" s="13">
         <v>12.3</v>
       </c>
-      <c r="I18" s="14">
+      <c r="I18" s="13">
         <v>12.03</v>
       </c>
-      <c r="J18" s="14">
+      <c r="J18" s="13">
         <v>28</v>
       </c>
-      <c r="K18" s="14">
+      <c r="K18" s="13">
         <v>699</v>
       </c>
     </row>
@@ -14140,16 +14305,16 @@
       <c r="G19" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H19" s="13">
         <v>12.31</v>
       </c>
-      <c r="I19" s="14">
+      <c r="I19" s="13">
         <v>12.1</v>
       </c>
-      <c r="J19" s="14">
+      <c r="J19" s="13">
         <v>15</v>
       </c>
-      <c r="K19" s="14">
+      <c r="K19" s="13">
         <v>699</v>
       </c>
     </row>
@@ -14175,16 +14340,16 @@
       <c r="G20" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="13">
         <v>12.28</v>
       </c>
-      <c r="I20" s="14">
+      <c r="I20" s="13">
         <v>11.55</v>
       </c>
-      <c r="J20" s="14">
-        <v>12</v>
-      </c>
-      <c r="K20" s="14">
+      <c r="J20" s="13">
+        <v>12</v>
+      </c>
+      <c r="K20" s="13">
         <v>610</v>
       </c>
     </row>
@@ -14210,16 +14375,16 @@
       <c r="G21" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H21" s="13">
         <v>12.33</v>
       </c>
-      <c r="I21" s="14">
+      <c r="I21" s="13">
         <v>12.15</v>
       </c>
-      <c r="J21" s="14">
+      <c r="J21" s="13">
         <v>21</v>
       </c>
-      <c r="K21" s="14">
+      <c r="K21" s="13">
         <v>604</v>
       </c>
     </row>
@@ -14245,16 +14410,16 @@
       <c r="G22" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H22" s="13">
         <v>12.3</v>
       </c>
-      <c r="I22" s="14">
+      <c r="I22" s="13">
         <v>11.33</v>
       </c>
-      <c r="J22" s="14">
+      <c r="J22" s="13">
         <v>34</v>
       </c>
-      <c r="K22" s="14">
+      <c r="K22" s="13">
         <v>542</v>
       </c>
     </row>
@@ -14280,16 +14445,16 @@
       <c r="G23" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H23" s="14">
+      <c r="H23" s="13">
         <v>12.15</v>
       </c>
-      <c r="I23" s="14">
+      <c r="I23" s="13">
         <v>11.52</v>
       </c>
-      <c r="J23" s="14">
-        <v>11</v>
-      </c>
-      <c r="K23" s="14">
+      <c r="J23" s="13">
+        <v>11</v>
+      </c>
+      <c r="K23" s="13">
         <v>549</v>
       </c>
     </row>
@@ -14315,16 +14480,16 @@
       <c r="G24" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H24" s="14">
+      <c r="H24" s="13">
         <v>12.34</v>
       </c>
-      <c r="I24" s="14">
+      <c r="I24" s="13">
         <v>11.49</v>
       </c>
-      <c r="J24" s="14">
+      <c r="J24" s="13">
         <v>24</v>
       </c>
-      <c r="K24" s="14">
+      <c r="K24" s="13">
         <v>546</v>
       </c>
     </row>
@@ -14350,16 +14515,16 @@
       <c r="G25" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H25" s="14">
+      <c r="H25" s="13">
         <v>12.21</v>
       </c>
-      <c r="I25" s="14">
+      <c r="I25" s="13">
         <v>11.59</v>
       </c>
-      <c r="J25" s="14">
+      <c r="J25" s="13">
         <v>18</v>
       </c>
-      <c r="K25" s="14">
+      <c r="K25" s="13">
         <v>698</v>
       </c>
     </row>
@@ -14385,16 +14550,16 @@
       <c r="G26" t="s" s="9">
         <v>11</v>
       </c>
-      <c r="H26" s="14">
+      <c r="H26" s="13">
         <v>0</v>
       </c>
-      <c r="I26" s="14">
+      <c r="I26" s="13">
         <v>0</v>
       </c>
-      <c r="J26" s="14">
+      <c r="J26" s="13">
         <v>0</v>
       </c>
-      <c r="K26" s="14">
+      <c r="K26" s="13">
         <v>699</v>
       </c>
     </row>
@@ -14420,16 +14585,16 @@
       <c r="G27" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H27" s="14">
+      <c r="H27" s="13">
         <v>12.21</v>
       </c>
-      <c r="I27" s="14">
+      <c r="I27" s="13">
         <v>12.05</v>
       </c>
-      <c r="J27" s="14">
-        <v>10</v>
-      </c>
-      <c r="K27" s="14">
+      <c r="J27" s="13">
+        <v>10</v>
+      </c>
+      <c r="K27" s="13">
         <v>699</v>
       </c>
     </row>
@@ -14455,16 +14620,16 @@
       <c r="G28" t="s" s="9">
         <v>11</v>
       </c>
-      <c r="H28" s="14">
+      <c r="H28" s="13">
         <v>11.07</v>
       </c>
-      <c r="I28" s="14">
+      <c r="I28" s="13">
         <v>9.289999999999999</v>
       </c>
-      <c r="J28" s="14">
+      <c r="J28" s="13">
         <v>92</v>
       </c>
-      <c r="K28" s="14">
+      <c r="K28" s="13">
         <v>698</v>
       </c>
     </row>
@@ -14490,16 +14655,16 @@
       <c r="G29" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H29" s="14">
+      <c r="H29" s="13">
         <v>12.29</v>
       </c>
-      <c r="I29" s="14">
+      <c r="I29" s="13">
         <v>11.24</v>
       </c>
-      <c r="J29" s="14">
+      <c r="J29" s="13">
         <v>36</v>
       </c>
-      <c r="K29" s="14">
+      <c r="K29" s="13">
         <v>699</v>
       </c>
     </row>
@@ -14525,16 +14690,16 @@
       <c r="G30" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H30" s="14">
+      <c r="H30" s="13">
         <v>12.13</v>
       </c>
-      <c r="I30" s="14">
+      <c r="I30" s="13">
         <v>10.33</v>
       </c>
-      <c r="J30" s="14">
+      <c r="J30" s="13">
         <v>56</v>
       </c>
-      <c r="K30" s="14">
+      <c r="K30" s="13">
         <v>699</v>
       </c>
     </row>
@@ -14556,12 +14721,12 @@
   <dimension ref="A1:K30"/>
   <sheetFormatPr defaultColWidth="9.16667" defaultRowHeight="15.4" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="2.67188" style="16" customWidth="1"/>
-    <col min="2" max="2" width="11" style="16" customWidth="1"/>
-    <col min="3" max="6" width="9.17188" style="16" customWidth="1"/>
-    <col min="7" max="7" width="9.85156" style="16" customWidth="1"/>
-    <col min="8" max="11" width="9.17188" style="16" customWidth="1"/>
-    <col min="12" max="16384" width="9.17188" style="16" customWidth="1"/>
+    <col min="1" max="1" width="2.67188" style="15" customWidth="1"/>
+    <col min="2" max="2" width="11" style="15" customWidth="1"/>
+    <col min="3" max="6" width="9.17188" style="15" customWidth="1"/>
+    <col min="7" max="7" width="9.85156" style="15" customWidth="1"/>
+    <col min="8" max="11" width="9.17188" style="15" customWidth="1"/>
+    <col min="12" max="16384" width="9.17188" style="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -14638,16 +14803,16 @@
       <c r="G3" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H3" s="14">
+      <c r="H3" s="13">
         <v>13</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="13">
         <v>12.15</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="13">
         <v>24</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="13">
         <v>547</v>
       </c>
     </row>
@@ -14673,16 +14838,16 @@
       <c r="G4" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="13">
         <v>13</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="13">
         <v>12.39</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="13">
         <v>19</v>
       </c>
-      <c r="K4" s="14">
+      <c r="K4" s="13">
         <v>547</v>
       </c>
     </row>
@@ -14708,16 +14873,16 @@
       <c r="G5" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="13">
         <v>13</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="13">
         <v>12.28</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="13">
         <v>33</v>
       </c>
-      <c r="K5" s="14">
+      <c r="K5" s="13">
         <v>544</v>
       </c>
     </row>
@@ -14743,16 +14908,16 @@
       <c r="G6" t="s" s="9">
         <v>9</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="13">
         <v>11.17</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="13">
         <v>9.369999999999999</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="13">
         <v>64</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="13">
         <v>545</v>
       </c>
     </row>
@@ -14778,16 +14943,16 @@
       <c r="G7" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="13">
         <v>12.54</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="13">
         <v>12.01</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="13">
         <v>33</v>
       </c>
-      <c r="K7" s="14">
+      <c r="K7" s="13">
         <v>546</v>
       </c>
     </row>
@@ -14813,16 +14978,16 @@
       <c r="G8" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="13">
         <v>13</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="13">
         <v>11.26</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="13">
         <v>51</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="13">
         <v>549</v>
       </c>
     </row>
@@ -14848,16 +15013,16 @@
       <c r="G9" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="13">
         <v>13</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="13">
         <v>12.49</v>
       </c>
-      <c r="J9" s="14">
+      <c r="J9" s="13">
         <v>9</v>
       </c>
-      <c r="K9" s="14">
+      <c r="K9" s="13">
         <v>699</v>
       </c>
     </row>
@@ -14883,16 +15048,16 @@
       <c r="G10" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="13">
         <v>12.53</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="13">
         <v>12.32</v>
       </c>
-      <c r="J10" s="14">
+      <c r="J10" s="13">
         <v>21</v>
       </c>
-      <c r="K10" s="14">
+      <c r="K10" s="13">
         <v>699</v>
       </c>
     </row>
@@ -14918,16 +15083,16 @@
       <c r="G11" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="13">
         <v>12.54</v>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="13">
         <v>12.09</v>
       </c>
-      <c r="J11" s="14">
+      <c r="J11" s="13">
         <v>30</v>
       </c>
-      <c r="K11" s="14">
+      <c r="K11" s="13">
         <v>699</v>
       </c>
     </row>
@@ -14953,16 +15118,16 @@
       <c r="G12" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="13">
         <v>13</v>
       </c>
-      <c r="I12" s="14">
+      <c r="I12" s="13">
         <v>12.38</v>
       </c>
-      <c r="J12" s="14">
+      <c r="J12" s="13">
         <v>18</v>
       </c>
-      <c r="K12" s="14">
+      <c r="K12" s="13">
         <v>698</v>
       </c>
     </row>
@@ -14988,16 +15153,16 @@
       <c r="G13" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="13">
         <v>13</v>
       </c>
-      <c r="I13" s="14">
+      <c r="I13" s="13">
         <v>12.26</v>
       </c>
-      <c r="J13" s="14">
+      <c r="J13" s="13">
         <v>18</v>
       </c>
-      <c r="K13" s="14">
+      <c r="K13" s="13">
         <v>699</v>
       </c>
     </row>
@@ -15023,16 +15188,16 @@
       <c r="G14" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="13">
         <v>12.55</v>
       </c>
-      <c r="I14" s="14">
+      <c r="I14" s="13">
         <v>12.26</v>
       </c>
-      <c r="J14" s="14">
+      <c r="J14" s="13">
         <v>26</v>
       </c>
-      <c r="K14" s="14">
+      <c r="K14" s="13">
         <v>697</v>
       </c>
     </row>
@@ -15058,16 +15223,16 @@
       <c r="G15" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H15" s="13">
         <v>12.55</v>
       </c>
-      <c r="I15" s="14">
+      <c r="I15" s="13">
         <v>11.54</v>
       </c>
-      <c r="J15" s="14">
+      <c r="J15" s="13">
         <v>55</v>
       </c>
-      <c r="K15" s="14">
+      <c r="K15" s="13">
         <v>699</v>
       </c>
     </row>
@@ -15093,16 +15258,16 @@
       <c r="G16" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="13">
         <v>12.54</v>
       </c>
-      <c r="I16" s="14">
+      <c r="I16" s="13">
         <v>12.06</v>
       </c>
-      <c r="J16" s="14">
+      <c r="J16" s="13">
         <v>28</v>
       </c>
-      <c r="K16" s="14">
+      <c r="K16" s="13">
         <v>698</v>
       </c>
     </row>
@@ -15128,16 +15293,16 @@
       <c r="G17" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H17" s="14">
+      <c r="H17" s="13">
         <v>13</v>
       </c>
-      <c r="I17" s="14">
+      <c r="I17" s="13">
         <v>12.23</v>
       </c>
-      <c r="J17" s="14">
+      <c r="J17" s="13">
         <v>40</v>
       </c>
-      <c r="K17" s="14">
+      <c r="K17" s="13">
         <v>699</v>
       </c>
     </row>
@@ -15163,16 +15328,16 @@
       <c r="G18" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H18" s="13">
         <v>12.56</v>
       </c>
-      <c r="I18" s="14">
+      <c r="I18" s="13">
         <v>12.28</v>
       </c>
-      <c r="J18" s="14">
+      <c r="J18" s="13">
         <v>33</v>
       </c>
-      <c r="K18" s="14">
+      <c r="K18" s="13">
         <v>699</v>
       </c>
     </row>
@@ -15198,16 +15363,16 @@
       <c r="G19" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H19" s="13">
         <v>13</v>
       </c>
-      <c r="I19" s="14">
+      <c r="I19" s="13">
         <v>12.36</v>
       </c>
-      <c r="J19" s="14">
+      <c r="J19" s="13">
         <v>16</v>
       </c>
-      <c r="K19" s="14">
+      <c r="K19" s="13">
         <v>699</v>
       </c>
     </row>
@@ -15233,16 +15398,16 @@
       <c r="G20" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="13">
         <v>13</v>
       </c>
-      <c r="I20" s="14">
+      <c r="I20" s="13">
         <v>12.39</v>
       </c>
-      <c r="J20" s="14">
+      <c r="J20" s="13">
         <v>14</v>
       </c>
-      <c r="K20" s="14">
+      <c r="K20" s="13">
         <v>610</v>
       </c>
     </row>
@@ -15268,16 +15433,16 @@
       <c r="G21" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H21" s="13">
         <v>12.36</v>
       </c>
-      <c r="I21" s="14">
+      <c r="I21" s="13">
         <v>11.11</v>
       </c>
-      <c r="J21" s="14">
+      <c r="J21" s="13">
         <v>61</v>
       </c>
-      <c r="K21" s="14">
+      <c r="K21" s="13">
         <v>604</v>
       </c>
     </row>
@@ -15303,16 +15468,16 @@
       <c r="G22" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H22" s="13">
         <v>12.43</v>
       </c>
-      <c r="I22" s="14">
+      <c r="I22" s="13">
         <v>12.11</v>
       </c>
-      <c r="J22" s="14">
+      <c r="J22" s="13">
         <v>27</v>
       </c>
-      <c r="K22" s="14">
+      <c r="K22" s="13">
         <v>542</v>
       </c>
     </row>
@@ -15338,16 +15503,16 @@
       <c r="G23" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H23" s="14">
+      <c r="H23" s="13">
         <v>12.48</v>
       </c>
-      <c r="I23" s="14">
+      <c r="I23" s="13">
         <v>12.31</v>
       </c>
-      <c r="J23" s="14">
-        <v>12</v>
-      </c>
-      <c r="K23" s="14">
+      <c r="J23" s="13">
+        <v>12</v>
+      </c>
+      <c r="K23" s="13">
         <v>549</v>
       </c>
     </row>
@@ -15373,16 +15538,16 @@
       <c r="G24" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H24" s="14">
+      <c r="H24" s="13">
         <v>0</v>
       </c>
-      <c r="I24" s="14">
+      <c r="I24" s="13">
         <v>0</v>
       </c>
-      <c r="J24" s="14">
+      <c r="J24" s="13">
         <v>0</v>
       </c>
-      <c r="K24" s="14">
+      <c r="K24" s="13">
         <v>546</v>
       </c>
     </row>
@@ -15408,16 +15573,16 @@
       <c r="G25" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H25" s="14">
+      <c r="H25" s="13">
         <v>13</v>
       </c>
-      <c r="I25" s="14">
+      <c r="I25" s="13">
         <v>12.27</v>
       </c>
-      <c r="J25" s="14">
+      <c r="J25" s="13">
         <v>22</v>
       </c>
-      <c r="K25" s="14">
+      <c r="K25" s="13">
         <v>698</v>
       </c>
     </row>
@@ -15443,16 +15608,16 @@
       <c r="G26" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H26" s="14">
+      <c r="H26" s="13">
         <v>5.26</v>
       </c>
-      <c r="I26" s="14">
+      <c r="I26" s="13">
         <v>3.12</v>
       </c>
-      <c r="J26" s="14">
+      <c r="J26" s="13">
         <v>9</v>
       </c>
-      <c r="K26" s="14">
+      <c r="K26" s="13">
         <v>699</v>
       </c>
     </row>
@@ -15478,16 +15643,16 @@
       <c r="G27" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H27" s="14">
+      <c r="H27" s="13">
         <v>13</v>
       </c>
-      <c r="I27" s="14">
+      <c r="I27" s="13">
         <v>12.23</v>
       </c>
-      <c r="J27" s="14">
+      <c r="J27" s="13">
         <v>18</v>
       </c>
-      <c r="K27" s="14">
+      <c r="K27" s="13">
         <v>699</v>
       </c>
     </row>
@@ -15513,16 +15678,16 @@
       <c r="G28" t="s" s="9">
         <v>11</v>
       </c>
-      <c r="H28" s="14">
+      <c r="H28" s="13">
         <v>12.58</v>
       </c>
-      <c r="I28" s="14">
+      <c r="I28" s="13">
         <v>10.56</v>
       </c>
-      <c r="J28" s="14">
+      <c r="J28" s="13">
         <v>57</v>
       </c>
-      <c r="K28" s="14">
+      <c r="K28" s="13">
         <v>698</v>
       </c>
     </row>
@@ -15548,16 +15713,16 @@
       <c r="G29" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H29" s="14">
+      <c r="H29" s="13">
         <v>12.47</v>
       </c>
-      <c r="I29" s="14">
+      <c r="I29" s="13">
         <v>11.43</v>
       </c>
-      <c r="J29" s="14">
+      <c r="J29" s="13">
         <v>50</v>
       </c>
-      <c r="K29" s="14">
+      <c r="K29" s="13">
         <v>699</v>
       </c>
     </row>
@@ -15583,16 +15748,16 @@
       <c r="G30" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H30" s="14">
+      <c r="H30" s="13">
         <v>12.23</v>
       </c>
-      <c r="I30" s="14">
+      <c r="I30" s="13">
         <v>10.34</v>
       </c>
-      <c r="J30" s="14">
+      <c r="J30" s="13">
         <v>48</v>
       </c>
-      <c r="K30" s="14">
+      <c r="K30" s="13">
         <v>699</v>
       </c>
     </row>
@@ -15614,12 +15779,12 @@
   <dimension ref="A1:K30"/>
   <sheetFormatPr defaultColWidth="9.16667" defaultRowHeight="15.4" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="2.67188" style="17" customWidth="1"/>
-    <col min="2" max="2" width="11" style="17" customWidth="1"/>
-    <col min="3" max="6" width="9.17188" style="17" customWidth="1"/>
-    <col min="7" max="7" width="9.85156" style="17" customWidth="1"/>
-    <col min="8" max="11" width="9.17188" style="17" customWidth="1"/>
-    <col min="12" max="16384" width="9.17188" style="17" customWidth="1"/>
+    <col min="1" max="1" width="2.67188" style="16" customWidth="1"/>
+    <col min="2" max="2" width="11" style="16" customWidth="1"/>
+    <col min="3" max="6" width="9.17188" style="16" customWidth="1"/>
+    <col min="7" max="7" width="9.85156" style="16" customWidth="1"/>
+    <col min="8" max="11" width="9.17188" style="16" customWidth="1"/>
+    <col min="12" max="16384" width="9.17188" style="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -15696,16 +15861,16 @@
       <c r="G3" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H3" s="14">
+      <c r="H3" s="13">
         <v>12.51</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="13">
         <v>11.19</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="13">
         <v>39</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="13">
         <v>547</v>
       </c>
     </row>
@@ -15731,16 +15896,16 @@
       <c r="G4" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="13">
         <v>12.47</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="13">
         <v>12.15</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="13">
         <v>26</v>
       </c>
-      <c r="K4" s="14">
+      <c r="K4" s="13">
         <v>547</v>
       </c>
     </row>
@@ -15766,16 +15931,16 @@
       <c r="G5" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="13">
         <v>13</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="13">
         <v>11.53</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="13">
         <v>45</v>
       </c>
-      <c r="K5" s="14">
+      <c r="K5" s="13">
         <v>544</v>
       </c>
     </row>
@@ -15801,16 +15966,16 @@
       <c r="G6" t="s" s="9">
         <v>9</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="13">
         <v>5.35</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="13">
         <v>3.41</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="13">
         <v>59</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="13">
         <v>545</v>
       </c>
     </row>
@@ -15836,16 +16001,16 @@
       <c r="G7" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="13">
         <v>12.49</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="13">
         <v>11.21</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="13">
         <v>46</v>
       </c>
-      <c r="K7" s="14">
+      <c r="K7" s="13">
         <v>546</v>
       </c>
     </row>
@@ -15871,16 +16036,16 @@
       <c r="G8" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="13">
         <v>13</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="13">
         <v>11.57</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="13">
         <v>29</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="13">
         <v>549</v>
       </c>
     </row>
@@ -15906,16 +16071,16 @@
       <c r="G9" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="13">
         <v>13</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="13">
         <v>12.47</v>
       </c>
-      <c r="J9" s="14">
+      <c r="J9" s="13">
         <v>6</v>
       </c>
-      <c r="K9" s="14">
+      <c r="K9" s="13">
         <v>699</v>
       </c>
     </row>
@@ -15941,16 +16106,16 @@
       <c r="G10" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="13">
         <v>13</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="13">
         <v>12.25</v>
       </c>
-      <c r="J10" s="14">
+      <c r="J10" s="13">
         <v>24</v>
       </c>
-      <c r="K10" s="14">
+      <c r="K10" s="13">
         <v>699</v>
       </c>
     </row>
@@ -15976,16 +16141,16 @@
       <c r="G11" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="13">
         <v>12.57</v>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="13">
         <v>12.27</v>
       </c>
-      <c r="J11" s="14">
+      <c r="J11" s="13">
         <v>18</v>
       </c>
-      <c r="K11" s="14">
+      <c r="K11" s="13">
         <v>699</v>
       </c>
     </row>
@@ -16011,16 +16176,16 @@
       <c r="G12" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="13">
         <v>12.56</v>
       </c>
-      <c r="I12" s="14">
+      <c r="I12" s="13">
         <v>12.27</v>
       </c>
-      <c r="J12" s="14">
+      <c r="J12" s="13">
         <v>19</v>
       </c>
-      <c r="K12" s="14">
+      <c r="K12" s="13">
         <v>698</v>
       </c>
     </row>
@@ -16046,16 +16211,16 @@
       <c r="G13" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H13" s="14">
-        <v>12</v>
-      </c>
-      <c r="I13" s="14">
+      <c r="H13" s="13">
+        <v>12</v>
+      </c>
+      <c r="I13" s="13">
         <v>10.34</v>
       </c>
-      <c r="J13" s="14">
+      <c r="J13" s="13">
         <v>57</v>
       </c>
-      <c r="K13" s="14">
+      <c r="K13" s="13">
         <v>699</v>
       </c>
     </row>
@@ -16081,16 +16246,16 @@
       <c r="G14" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="13">
         <v>12.54</v>
       </c>
-      <c r="I14" s="14">
+      <c r="I14" s="13">
         <v>12.26</v>
       </c>
-      <c r="J14" s="14">
+      <c r="J14" s="13">
         <v>24</v>
       </c>
-      <c r="K14" s="14">
+      <c r="K14" s="13">
         <v>697</v>
       </c>
     </row>
@@ -16116,16 +16281,16 @@
       <c r="G15" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H15" s="13">
         <v>12.27</v>
       </c>
-      <c r="I15" s="14">
+      <c r="I15" s="13">
         <v>11.25</v>
       </c>
-      <c r="J15" s="14">
+      <c r="J15" s="13">
         <v>28</v>
       </c>
-      <c r="K15" s="14">
+      <c r="K15" s="13">
         <v>699</v>
       </c>
     </row>
@@ -16151,16 +16316,16 @@
       <c r="G16" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="13">
         <v>12.53</v>
       </c>
-      <c r="I16" s="14">
+      <c r="I16" s="13">
         <v>12.12</v>
       </c>
-      <c r="J16" s="14">
+      <c r="J16" s="13">
         <v>32</v>
       </c>
-      <c r="K16" s="14">
+      <c r="K16" s="13">
         <v>698</v>
       </c>
     </row>
@@ -16186,16 +16351,16 @@
       <c r="G17" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H17" s="14">
+      <c r="H17" s="13">
         <v>13</v>
       </c>
-      <c r="I17" s="14">
+      <c r="I17" s="13">
         <v>12.18</v>
       </c>
-      <c r="J17" s="14">
+      <c r="J17" s="13">
         <v>32</v>
       </c>
-      <c r="K17" s="14">
+      <c r="K17" s="13">
         <v>699</v>
       </c>
     </row>
@@ -16221,16 +16386,16 @@
       <c r="G18" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H18" s="13">
         <v>12.58</v>
       </c>
-      <c r="I18" s="14">
+      <c r="I18" s="13">
         <v>12.05</v>
       </c>
-      <c r="J18" s="14">
+      <c r="J18" s="13">
         <v>28</v>
       </c>
-      <c r="K18" s="14">
+      <c r="K18" s="13">
         <v>699</v>
       </c>
     </row>
@@ -16256,16 +16421,16 @@
       <c r="G19" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H19" s="13">
         <v>13</v>
       </c>
-      <c r="I19" s="14">
+      <c r="I19" s="13">
         <v>12.17</v>
       </c>
-      <c r="J19" s="14">
+      <c r="J19" s="13">
         <v>30</v>
       </c>
-      <c r="K19" s="14">
+      <c r="K19" s="13">
         <v>699</v>
       </c>
     </row>
@@ -16291,16 +16456,16 @@
       <c r="G20" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="13">
         <v>13</v>
       </c>
-      <c r="I20" s="14">
+      <c r="I20" s="13">
         <v>12.02</v>
       </c>
-      <c r="J20" s="14">
+      <c r="J20" s="13">
         <v>35</v>
       </c>
-      <c r="K20" s="14">
+      <c r="K20" s="13">
         <v>610</v>
       </c>
     </row>
@@ -16326,16 +16491,16 @@
       <c r="G21" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H21" s="13">
         <v>12.53</v>
       </c>
-      <c r="I21" s="14">
+      <c r="I21" s="13">
         <v>11.46</v>
       </c>
-      <c r="J21" s="14">
+      <c r="J21" s="13">
         <v>46</v>
       </c>
-      <c r="K21" s="14">
+      <c r="K21" s="13">
         <v>604</v>
       </c>
     </row>
@@ -16361,16 +16526,16 @@
       <c r="G22" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H22" s="13">
         <v>13</v>
       </c>
-      <c r="I22" s="14">
+      <c r="I22" s="13">
         <v>12.39</v>
       </c>
-      <c r="J22" s="14">
+      <c r="J22" s="13">
         <v>13</v>
       </c>
-      <c r="K22" s="14">
+      <c r="K22" s="13">
         <v>542</v>
       </c>
     </row>
@@ -16396,16 +16561,16 @@
       <c r="G23" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H23" s="14">
+      <c r="H23" s="13">
         <v>12.51</v>
       </c>
-      <c r="I23" s="14">
+      <c r="I23" s="13">
         <v>12.37</v>
       </c>
-      <c r="J23" s="14">
+      <c r="J23" s="13">
         <v>7</v>
       </c>
-      <c r="K23" s="14">
+      <c r="K23" s="13">
         <v>549</v>
       </c>
     </row>
@@ -16431,16 +16596,16 @@
       <c r="G24" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H24" s="14">
+      <c r="H24" s="13">
         <v>5.16</v>
       </c>
-      <c r="I24" s="14">
+      <c r="I24" s="13">
         <v>3.44</v>
       </c>
-      <c r="J24" s="14">
-        <v>11</v>
-      </c>
-      <c r="K24" s="14">
+      <c r="J24" s="13">
+        <v>11</v>
+      </c>
+      <c r="K24" s="13">
         <v>546</v>
       </c>
     </row>
@@ -16466,16 +16631,16 @@
       <c r="G25" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H25" s="14">
+      <c r="H25" s="13">
         <v>12.54</v>
       </c>
-      <c r="I25" s="14">
+      <c r="I25" s="13">
         <v>12.19</v>
       </c>
-      <c r="J25" s="14">
+      <c r="J25" s="13">
         <v>21</v>
       </c>
-      <c r="K25" s="14">
+      <c r="K25" s="13">
         <v>698</v>
       </c>
     </row>
@@ -16501,16 +16666,16 @@
       <c r="G26" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H26" s="14">
+      <c r="H26" s="13">
         <v>12.51</v>
       </c>
-      <c r="I26" s="14">
+      <c r="I26" s="13">
         <v>11.21</v>
       </c>
-      <c r="J26" s="14">
+      <c r="J26" s="13">
         <v>46</v>
       </c>
-      <c r="K26" s="14">
+      <c r="K26" s="13">
         <v>699</v>
       </c>
     </row>
@@ -16536,16 +16701,16 @@
       <c r="G27" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H27" s="14">
+      <c r="H27" s="13">
         <v>12.47</v>
       </c>
-      <c r="I27" s="14">
+      <c r="I27" s="13">
         <v>10.56</v>
       </c>
-      <c r="J27" s="14">
+      <c r="J27" s="13">
         <v>67</v>
       </c>
-      <c r="K27" s="14">
+      <c r="K27" s="13">
         <v>699</v>
       </c>
     </row>
@@ -16571,16 +16736,16 @@
       <c r="G28" t="s" s="9">
         <v>11</v>
       </c>
-      <c r="H28" s="14">
+      <c r="H28" s="13">
         <v>12.51</v>
       </c>
-      <c r="I28" s="14">
+      <c r="I28" s="13">
         <v>9.470000000000001</v>
       </c>
-      <c r="J28" s="14">
+      <c r="J28" s="13">
         <v>141</v>
       </c>
-      <c r="K28" s="14">
+      <c r="K28" s="13">
         <v>698</v>
       </c>
     </row>
@@ -16606,16 +16771,16 @@
       <c r="G29" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H29" s="14">
+      <c r="H29" s="13">
         <v>12.59</v>
       </c>
-      <c r="I29" s="14">
+      <c r="I29" s="13">
         <v>10.12</v>
       </c>
-      <c r="J29" s="14">
+      <c r="J29" s="13">
         <v>86</v>
       </c>
-      <c r="K29" s="14">
+      <c r="K29" s="13">
         <v>699</v>
       </c>
     </row>
@@ -16641,16 +16806,16 @@
       <c r="G30" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H30" s="14">
+      <c r="H30" s="13">
         <v>12.52</v>
       </c>
-      <c r="I30" s="14">
+      <c r="I30" s="13">
         <v>10.42</v>
       </c>
-      <c r="J30" s="14">
+      <c r="J30" s="13">
         <v>74</v>
       </c>
-      <c r="K30" s="14">
+      <c r="K30" s="13">
         <v>699</v>
       </c>
     </row>
@@ -16672,12 +16837,12 @@
   <dimension ref="A1:K30"/>
   <sheetFormatPr defaultColWidth="9.16667" defaultRowHeight="15.4" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="2.67188" style="18" customWidth="1"/>
-    <col min="2" max="2" width="11" style="18" customWidth="1"/>
-    <col min="3" max="6" width="9.17188" style="18" customWidth="1"/>
-    <col min="7" max="7" width="9.85156" style="18" customWidth="1"/>
-    <col min="8" max="11" width="9.17188" style="18" customWidth="1"/>
-    <col min="12" max="16384" width="9.17188" style="18" customWidth="1"/>
+    <col min="1" max="1" width="2.67188" style="17" customWidth="1"/>
+    <col min="2" max="2" width="11" style="17" customWidth="1"/>
+    <col min="3" max="6" width="9.17188" style="17" customWidth="1"/>
+    <col min="7" max="7" width="9.85156" style="17" customWidth="1"/>
+    <col min="8" max="11" width="9.17188" style="17" customWidth="1"/>
+    <col min="12" max="16384" width="9.17188" style="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -16754,16 +16919,16 @@
       <c r="G3" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H3" s="14">
+      <c r="H3" s="13">
         <v>13</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="13">
         <v>11.33</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="13">
         <v>46</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="13">
         <v>547</v>
       </c>
     </row>
@@ -16789,16 +16954,16 @@
       <c r="G4" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="13">
         <v>13</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="13">
         <v>12.34</v>
       </c>
-      <c r="J4" s="14">
-        <v>10</v>
-      </c>
-      <c r="K4" s="14">
+      <c r="J4" s="13">
+        <v>10</v>
+      </c>
+      <c r="K4" s="13">
         <v>547</v>
       </c>
     </row>
@@ -16824,16 +16989,16 @@
       <c r="G5" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="13">
         <v>13</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="13">
         <v>12.22</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="13">
         <v>21</v>
       </c>
-      <c r="K5" s="14">
+      <c r="K5" s="13">
         <v>544</v>
       </c>
     </row>
@@ -16859,16 +17024,16 @@
       <c r="G6" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="13">
         <v>3.29</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="13">
         <v>3.02</v>
       </c>
-      <c r="J6" s="14">
-        <v>12</v>
-      </c>
-      <c r="K6" s="14">
+      <c r="J6" s="13">
+        <v>12</v>
+      </c>
+      <c r="K6" s="13">
         <v>545</v>
       </c>
     </row>
@@ -16894,16 +17059,16 @@
       <c r="G7" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="13">
         <v>12.57</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="13">
         <v>11.59</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="13">
         <v>31</v>
       </c>
-      <c r="K7" s="14">
+      <c r="K7" s="13">
         <v>546</v>
       </c>
     </row>
@@ -16929,16 +17094,16 @@
       <c r="G8" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H8" s="14">
-        <v>12</v>
-      </c>
-      <c r="I8" s="14">
+      <c r="H8" s="13">
+        <v>12</v>
+      </c>
+      <c r="I8" s="13">
         <v>7.31</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="13">
         <v>61</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="13">
         <v>549</v>
       </c>
     </row>
@@ -16964,16 +17129,16 @@
       <c r="G9" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="13">
         <v>12.48</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="13">
         <v>12.15</v>
       </c>
-      <c r="J9" s="14">
-        <v>12</v>
-      </c>
-      <c r="K9" s="14">
+      <c r="J9" s="13">
+        <v>12</v>
+      </c>
+      <c r="K9" s="13">
         <v>699</v>
       </c>
     </row>
@@ -16999,16 +17164,16 @@
       <c r="G10" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="13">
         <v>13</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="13">
         <v>12.27</v>
       </c>
-      <c r="J10" s="14">
+      <c r="J10" s="13">
         <v>14</v>
       </c>
-      <c r="K10" s="14">
+      <c r="K10" s="13">
         <v>699</v>
       </c>
     </row>
@@ -17034,16 +17199,16 @@
       <c r="G11" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="13">
         <v>12.44</v>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="13">
         <v>12.2</v>
       </c>
-      <c r="J11" s="14">
+      <c r="J11" s="13">
         <v>16</v>
       </c>
-      <c r="K11" s="14">
+      <c r="K11" s="13">
         <v>699</v>
       </c>
     </row>
@@ -17069,16 +17234,16 @@
       <c r="G12" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="13">
         <v>12.54</v>
       </c>
-      <c r="I12" s="14">
+      <c r="I12" s="13">
         <v>12.43</v>
       </c>
-      <c r="J12" s="14">
-        <v>12</v>
-      </c>
-      <c r="K12" s="14">
+      <c r="J12" s="13">
+        <v>12</v>
+      </c>
+      <c r="K12" s="13">
         <v>698</v>
       </c>
     </row>
@@ -17104,16 +17269,16 @@
       <c r="G13" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="13">
         <v>13</v>
       </c>
-      <c r="I13" s="14">
+      <c r="I13" s="13">
         <v>12.17</v>
       </c>
-      <c r="J13" s="14">
+      <c r="J13" s="13">
         <v>26</v>
       </c>
-      <c r="K13" s="14">
+      <c r="K13" s="13">
         <v>699</v>
       </c>
     </row>
@@ -17139,16 +17304,16 @@
       <c r="G14" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="13">
         <v>12.5</v>
       </c>
-      <c r="I14" s="14">
+      <c r="I14" s="13">
         <v>11.58</v>
       </c>
-      <c r="J14" s="14">
+      <c r="J14" s="13">
         <v>38</v>
       </c>
-      <c r="K14" s="14">
+      <c r="K14" s="13">
         <v>697</v>
       </c>
     </row>
@@ -17174,16 +17339,16 @@
       <c r="G15" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H15" s="13">
         <v>12.48</v>
       </c>
-      <c r="I15" s="14">
+      <c r="I15" s="13">
         <v>12.04</v>
       </c>
-      <c r="J15" s="14">
+      <c r="J15" s="13">
         <v>29</v>
       </c>
-      <c r="K15" s="14">
+      <c r="K15" s="13">
         <v>699</v>
       </c>
     </row>
@@ -17209,16 +17374,16 @@
       <c r="G16" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="13">
         <v>13</v>
       </c>
-      <c r="I16" s="14">
+      <c r="I16" s="13">
         <v>12.31</v>
       </c>
-      <c r="J16" s="14">
+      <c r="J16" s="13">
         <v>18</v>
       </c>
-      <c r="K16" s="14">
+      <c r="K16" s="13">
         <v>698</v>
       </c>
     </row>
@@ -17244,16 +17409,16 @@
       <c r="G17" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H17" s="14">
+      <c r="H17" s="13">
         <v>12.58</v>
       </c>
-      <c r="I17" s="14">
+      <c r="I17" s="13">
         <v>12.32</v>
       </c>
-      <c r="J17" s="14">
+      <c r="J17" s="13">
         <v>21</v>
       </c>
-      <c r="K17" s="14">
+      <c r="K17" s="13">
         <v>699</v>
       </c>
     </row>
@@ -17279,16 +17444,16 @@
       <c r="G18" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H18" s="13">
         <v>12.47</v>
       </c>
-      <c r="I18" s="14">
+      <c r="I18" s="13">
         <v>11.54</v>
       </c>
-      <c r="J18" s="14">
+      <c r="J18" s="13">
         <v>33</v>
       </c>
-      <c r="K18" s="14">
+      <c r="K18" s="13">
         <v>699</v>
       </c>
     </row>
@@ -17314,16 +17479,16 @@
       <c r="G19" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H19" s="13">
         <v>12.56</v>
       </c>
-      <c r="I19" s="14">
+      <c r="I19" s="13">
         <v>12.27</v>
       </c>
-      <c r="J19" s="14">
+      <c r="J19" s="13">
         <v>22</v>
       </c>
-      <c r="K19" s="14">
+      <c r="K19" s="13">
         <v>699</v>
       </c>
     </row>
@@ -17349,16 +17514,16 @@
       <c r="G20" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="13">
         <v>13</v>
       </c>
-      <c r="I20" s="14">
+      <c r="I20" s="13">
         <v>12.17</v>
       </c>
-      <c r="J20" s="14">
+      <c r="J20" s="13">
         <v>27</v>
       </c>
-      <c r="K20" s="14">
+      <c r="K20" s="13">
         <v>610</v>
       </c>
     </row>
@@ -17384,16 +17549,16 @@
       <c r="G21" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H21" s="13">
         <v>12.54</v>
       </c>
-      <c r="I21" s="14">
+      <c r="I21" s="13">
         <v>11.21</v>
       </c>
-      <c r="J21" s="14">
+      <c r="J21" s="13">
         <v>52</v>
       </c>
-      <c r="K21" s="14">
+      <c r="K21" s="13">
         <v>604</v>
       </c>
     </row>
@@ -17419,16 +17584,16 @@
       <c r="G22" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H22" s="13">
         <v>13</v>
       </c>
-      <c r="I22" s="14">
+      <c r="I22" s="13">
         <v>12.49</v>
       </c>
-      <c r="J22" s="14">
-        <v>11</v>
-      </c>
-      <c r="K22" s="14">
+      <c r="J22" s="13">
+        <v>11</v>
+      </c>
+      <c r="K22" s="13">
         <v>542</v>
       </c>
     </row>
@@ -17454,16 +17619,16 @@
       <c r="G23" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H23" s="14">
+      <c r="H23" s="13">
         <v>13</v>
       </c>
-      <c r="I23" s="14">
+      <c r="I23" s="13">
         <v>12.4</v>
       </c>
-      <c r="J23" s="14">
+      <c r="J23" s="13">
         <v>15</v>
       </c>
-      <c r="K23" s="14">
+      <c r="K23" s="13">
         <v>549</v>
       </c>
     </row>
@@ -17489,16 +17654,16 @@
       <c r="G24" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H24" s="14">
+      <c r="H24" s="13">
         <v>13</v>
       </c>
-      <c r="I24" s="14">
+      <c r="I24" s="13">
         <v>12.42</v>
       </c>
-      <c r="J24" s="14">
-        <v>12</v>
-      </c>
-      <c r="K24" s="14">
+      <c r="J24" s="13">
+        <v>12</v>
+      </c>
+      <c r="K24" s="13">
         <v>546</v>
       </c>
     </row>
@@ -17524,16 +17689,16 @@
       <c r="G25" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H25" s="14">
+      <c r="H25" s="13">
         <v>12.36</v>
       </c>
-      <c r="I25" s="14">
+      <c r="I25" s="13">
         <v>12.08</v>
       </c>
-      <c r="J25" s="14">
+      <c r="J25" s="13">
         <v>18</v>
       </c>
-      <c r="K25" s="14">
+      <c r="K25" s="13">
         <v>698</v>
       </c>
     </row>
@@ -17559,16 +17724,16 @@
       <c r="G26" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H26" s="14">
+      <c r="H26" s="13">
         <v>12.44</v>
       </c>
-      <c r="I26" s="14">
+      <c r="I26" s="13">
         <v>11.53</v>
       </c>
-      <c r="J26" s="14">
+      <c r="J26" s="13">
         <v>46</v>
       </c>
-      <c r="K26" s="14">
+      <c r="K26" s="13">
         <v>699</v>
       </c>
     </row>
@@ -17594,16 +17759,16 @@
       <c r="G27" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H27" s="14">
+      <c r="H27" s="13">
         <v>12.39</v>
       </c>
-      <c r="I27" s="14">
-        <v>12</v>
-      </c>
-      <c r="J27" s="14">
+      <c r="I27" s="13">
+        <v>12</v>
+      </c>
+      <c r="J27" s="13">
         <v>30</v>
       </c>
-      <c r="K27" s="14">
+      <c r="K27" s="13">
         <v>699</v>
       </c>
     </row>
@@ -17629,16 +17794,16 @@
       <c r="G28" t="s" s="9">
         <v>11</v>
       </c>
-      <c r="H28" s="14">
+      <c r="H28" s="13">
         <v>4.49</v>
       </c>
-      <c r="I28" s="14">
+      <c r="I28" s="13">
         <v>2.25</v>
       </c>
-      <c r="J28" s="14">
+      <c r="J28" s="13">
         <v>80</v>
       </c>
-      <c r="K28" s="14">
+      <c r="K28" s="13">
         <v>698</v>
       </c>
     </row>
@@ -17664,16 +17829,16 @@
       <c r="G29" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H29" s="14">
+      <c r="H29" s="13">
         <v>10.46</v>
       </c>
-      <c r="I29" s="14">
+      <c r="I29" s="13">
         <v>8.23</v>
       </c>
-      <c r="J29" s="14">
+      <c r="J29" s="13">
         <v>106</v>
       </c>
-      <c r="K29" s="14">
+      <c r="K29" s="13">
         <v>699</v>
       </c>
     </row>
@@ -17699,16 +17864,16 @@
       <c r="G30" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H30" s="14">
+      <c r="H30" s="13">
         <v>13</v>
       </c>
-      <c r="I30" s="14">
+      <c r="I30" s="13">
         <v>12.11</v>
       </c>
-      <c r="J30" s="14">
+      <c r="J30" s="13">
         <v>23</v>
       </c>
-      <c r="K30" s="14">
+      <c r="K30" s="13">
         <v>699</v>
       </c>
     </row>
@@ -17730,12 +17895,12 @@
   <dimension ref="A1:K30"/>
   <sheetFormatPr defaultColWidth="9.16667" defaultRowHeight="15.4" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="2.67188" style="19" customWidth="1"/>
-    <col min="2" max="2" width="11" style="19" customWidth="1"/>
-    <col min="3" max="6" width="9.17188" style="19" customWidth="1"/>
-    <col min="7" max="7" width="9.85156" style="19" customWidth="1"/>
-    <col min="8" max="11" width="9.17188" style="19" customWidth="1"/>
-    <col min="12" max="16384" width="9.17188" style="19" customWidth="1"/>
+    <col min="1" max="1" width="2.67188" style="18" customWidth="1"/>
+    <col min="2" max="2" width="11" style="18" customWidth="1"/>
+    <col min="3" max="6" width="9.17188" style="18" customWidth="1"/>
+    <col min="7" max="7" width="9.85156" style="18" customWidth="1"/>
+    <col min="8" max="11" width="9.17188" style="18" customWidth="1"/>
+    <col min="12" max="16384" width="9.17188" style="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -17812,16 +17977,16 @@
       <c r="G3" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H3" s="14">
+      <c r="H3" s="13">
         <v>13</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="13">
         <v>12.34</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="13">
         <v>25</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="13">
         <v>547</v>
       </c>
     </row>
@@ -17847,16 +18012,16 @@
       <c r="G4" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="13">
         <v>13</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="13">
         <v>12.47</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="13">
         <v>13</v>
       </c>
-      <c r="K4" s="14">
+      <c r="K4" s="13">
         <v>547</v>
       </c>
     </row>
@@ -17882,16 +18047,16 @@
       <c r="G5" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="13">
         <v>12.37</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="13">
         <v>10.58</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="13">
         <v>69</v>
       </c>
-      <c r="K5" s="14">
+      <c r="K5" s="13">
         <v>544</v>
       </c>
     </row>
@@ -17917,16 +18082,16 @@
       <c r="G6" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="13">
         <v>12.51</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="13">
         <v>11.34</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="13">
         <v>42</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="13">
         <v>545</v>
       </c>
     </row>
@@ -17952,16 +18117,16 @@
       <c r="G7" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="13">
         <v>13</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="13">
         <v>12.15</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="13">
         <v>27</v>
       </c>
-      <c r="K7" s="14">
+      <c r="K7" s="13">
         <v>546</v>
       </c>
     </row>
@@ -17987,16 +18152,16 @@
       <c r="G8" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="13">
         <v>12.44</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="13">
         <v>10.59</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="13">
         <v>56</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="13">
         <v>549</v>
       </c>
     </row>
@@ -18022,16 +18187,16 @@
       <c r="G9" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="13">
         <v>13</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="13">
         <v>12.39</v>
       </c>
-      <c r="J9" s="14">
+      <c r="J9" s="13">
         <v>7</v>
       </c>
-      <c r="K9" s="14">
+      <c r="K9" s="13">
         <v>699</v>
       </c>
     </row>
@@ -18057,16 +18222,16 @@
       <c r="G10" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="13">
         <v>12.52</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="13">
         <v>12.29</v>
       </c>
-      <c r="J10" s="14">
-        <v>11</v>
-      </c>
-      <c r="K10" s="14">
+      <c r="J10" s="13">
+        <v>11</v>
+      </c>
+      <c r="K10" s="13">
         <v>699</v>
       </c>
     </row>
@@ -18092,16 +18257,16 @@
       <c r="G11" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="13">
         <v>12.47</v>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="13">
         <v>12.34</v>
       </c>
-      <c r="J11" s="14">
-        <v>10</v>
-      </c>
-      <c r="K11" s="14">
+      <c r="J11" s="13">
+        <v>10</v>
+      </c>
+      <c r="K11" s="13">
         <v>699</v>
       </c>
     </row>
@@ -18127,16 +18292,16 @@
       <c r="G12" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="13">
         <v>12.57</v>
       </c>
-      <c r="I12" s="14">
+      <c r="I12" s="13">
         <v>12.34</v>
       </c>
-      <c r="J12" s="14">
+      <c r="J12" s="13">
         <v>20</v>
       </c>
-      <c r="K12" s="14">
+      <c r="K12" s="13">
         <v>698</v>
       </c>
     </row>
@@ -18162,16 +18327,16 @@
       <c r="G13" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="13">
         <v>13</v>
       </c>
-      <c r="I13" s="14">
+      <c r="I13" s="13">
         <v>12.22</v>
       </c>
-      <c r="J13" s="14">
+      <c r="J13" s="13">
         <v>28</v>
       </c>
-      <c r="K13" s="14">
+      <c r="K13" s="13">
         <v>699</v>
       </c>
     </row>
@@ -18197,16 +18362,16 @@
       <c r="G14" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="13">
         <v>12.44</v>
       </c>
-      <c r="I14" s="14">
+      <c r="I14" s="13">
         <v>11.59</v>
       </c>
-      <c r="J14" s="14">
+      <c r="J14" s="13">
         <v>44</v>
       </c>
-      <c r="K14" s="14">
+      <c r="K14" s="13">
         <v>697</v>
       </c>
     </row>
@@ -18232,16 +18397,16 @@
       <c r="G15" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H15" s="13">
         <v>12.53</v>
       </c>
-      <c r="I15" s="14">
+      <c r="I15" s="13">
         <v>12.4</v>
       </c>
-      <c r="J15" s="14">
+      <c r="J15" s="13">
         <v>14</v>
       </c>
-      <c r="K15" s="14">
+      <c r="K15" s="13">
         <v>699</v>
       </c>
     </row>
@@ -18267,16 +18432,16 @@
       <c r="G16" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="13">
         <v>11.38</v>
       </c>
-      <c r="I16" s="14">
+      <c r="I16" s="13">
         <v>10.29</v>
       </c>
-      <c r="J16" s="14">
+      <c r="J16" s="13">
         <v>40</v>
       </c>
-      <c r="K16" s="14">
+      <c r="K16" s="13">
         <v>698</v>
       </c>
     </row>
@@ -18302,16 +18467,16 @@
       <c r="G17" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H17" s="14">
+      <c r="H17" s="13">
         <v>13</v>
       </c>
-      <c r="I17" s="14">
+      <c r="I17" s="13">
         <v>12.43</v>
       </c>
-      <c r="J17" s="14">
+      <c r="J17" s="13">
         <v>24</v>
       </c>
-      <c r="K17" s="14">
+      <c r="K17" s="13">
         <v>699</v>
       </c>
     </row>
@@ -18337,16 +18502,16 @@
       <c r="G18" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H18" s="13">
         <v>12.51</v>
       </c>
-      <c r="I18" s="14">
+      <c r="I18" s="13">
         <v>12.04</v>
       </c>
-      <c r="J18" s="14">
+      <c r="J18" s="13">
         <v>34</v>
       </c>
-      <c r="K18" s="14">
+      <c r="K18" s="13">
         <v>699</v>
       </c>
     </row>
@@ -18372,16 +18537,16 @@
       <c r="G19" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H19" s="13">
         <v>12.55</v>
       </c>
-      <c r="I19" s="14">
+      <c r="I19" s="13">
         <v>12.22</v>
       </c>
-      <c r="J19" s="14">
+      <c r="J19" s="13">
         <v>21</v>
       </c>
-      <c r="K19" s="14">
+      <c r="K19" s="13">
         <v>699</v>
       </c>
     </row>
@@ -18407,16 +18572,16 @@
       <c r="G20" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="13">
         <v>13</v>
       </c>
-      <c r="I20" s="14">
+      <c r="I20" s="13">
         <v>11.55</v>
       </c>
-      <c r="J20" s="14">
+      <c r="J20" s="13">
         <v>39</v>
       </c>
-      <c r="K20" s="14">
+      <c r="K20" s="13">
         <v>610</v>
       </c>
     </row>
@@ -18442,16 +18607,16 @@
       <c r="G21" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H21" s="13">
         <v>13</v>
       </c>
-      <c r="I21" s="14">
-        <v>11</v>
-      </c>
-      <c r="J21" s="14">
+      <c r="I21" s="13">
+        <v>11</v>
+      </c>
+      <c r="J21" s="13">
         <v>90</v>
       </c>
-      <c r="K21" s="14">
+      <c r="K21" s="13">
         <v>604</v>
       </c>
     </row>
@@ -18477,16 +18642,16 @@
       <c r="G22" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H22" s="13">
         <v>7.19</v>
       </c>
-      <c r="I22" s="14">
+      <c r="I22" s="13">
         <v>7.12</v>
       </c>
-      <c r="J22" s="14">
+      <c r="J22" s="13">
         <v>3</v>
       </c>
-      <c r="K22" s="14">
+      <c r="K22" s="13">
         <v>542</v>
       </c>
     </row>
@@ -18512,16 +18677,16 @@
       <c r="G23" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H23" s="14">
+      <c r="H23" s="13">
         <v>13</v>
       </c>
-      <c r="I23" s="14">
+      <c r="I23" s="13">
         <v>12.53</v>
       </c>
-      <c r="J23" s="14">
+      <c r="J23" s="13">
         <v>4</v>
       </c>
-      <c r="K23" s="14">
+      <c r="K23" s="13">
         <v>549</v>
       </c>
     </row>
@@ -18547,16 +18712,16 @@
       <c r="G24" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H24" s="14">
+      <c r="H24" s="13">
         <v>12.48</v>
       </c>
-      <c r="I24" s="14">
+      <c r="I24" s="13">
         <v>12.22</v>
       </c>
-      <c r="J24" s="14">
-        <v>12</v>
-      </c>
-      <c r="K24" s="14">
+      <c r="J24" s="13">
+        <v>12</v>
+      </c>
+      <c r="K24" s="13">
         <v>546</v>
       </c>
     </row>
@@ -18582,16 +18747,16 @@
       <c r="G25" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H25" s="14">
+      <c r="H25" s="13">
         <v>13</v>
       </c>
-      <c r="I25" s="14">
+      <c r="I25" s="13">
         <v>12.47</v>
       </c>
-      <c r="J25" s="14">
-        <v>12</v>
-      </c>
-      <c r="K25" s="14">
+      <c r="J25" s="13">
+        <v>12</v>
+      </c>
+      <c r="K25" s="13">
         <v>698</v>
       </c>
     </row>
@@ -18617,16 +18782,16 @@
       <c r="G26" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H26" s="14">
+      <c r="H26" s="13">
         <v>13</v>
       </c>
-      <c r="I26" s="14">
+      <c r="I26" s="13">
         <v>12.36</v>
       </c>
-      <c r="J26" s="14">
+      <c r="J26" s="13">
         <v>31</v>
       </c>
-      <c r="K26" s="14">
+      <c r="K26" s="13">
         <v>699</v>
       </c>
     </row>
@@ -18652,16 +18817,16 @@
       <c r="G27" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H27" s="14">
+      <c r="H27" s="13">
         <v>12.34</v>
       </c>
-      <c r="I27" s="14">
+      <c r="I27" s="13">
         <v>11.27</v>
       </c>
-      <c r="J27" s="14">
+      <c r="J27" s="13">
         <v>53</v>
       </c>
-      <c r="K27" s="14">
+      <c r="K27" s="13">
         <v>699</v>
       </c>
     </row>
@@ -18687,16 +18852,16 @@
       <c r="G28" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H28" s="14">
+      <c r="H28" s="13">
         <v>6.2</v>
       </c>
-      <c r="I28" s="14">
+      <c r="I28" s="13">
         <v>5.31</v>
       </c>
-      <c r="J28" s="14">
+      <c r="J28" s="13">
         <v>35</v>
       </c>
-      <c r="K28" s="14">
+      <c r="K28" s="13">
         <v>698</v>
       </c>
     </row>
@@ -18722,16 +18887,16 @@
       <c r="G29" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H29" s="14">
+      <c r="H29" s="13">
         <v>12.51</v>
       </c>
-      <c r="I29" s="14">
-        <v>12</v>
-      </c>
-      <c r="J29" s="14">
+      <c r="I29" s="13">
+        <v>12</v>
+      </c>
+      <c r="J29" s="13">
         <v>33</v>
       </c>
-      <c r="K29" s="14">
+      <c r="K29" s="13">
         <v>699</v>
       </c>
     </row>
@@ -18757,16 +18922,16 @@
       <c r="G30" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H30" s="14">
+      <c r="H30" s="13">
         <v>13</v>
       </c>
-      <c r="I30" s="14">
+      <c r="I30" s="13">
         <v>11.57</v>
       </c>
-      <c r="J30" s="14">
+      <c r="J30" s="13">
         <v>22</v>
       </c>
-      <c r="K30" s="14">
+      <c r="K30" s="13">
         <v>699</v>
       </c>
     </row>
@@ -18788,12 +18953,12 @@
   <dimension ref="A1:K30"/>
   <sheetFormatPr defaultColWidth="9.16667" defaultRowHeight="15.4" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="2.67188" style="20" customWidth="1"/>
-    <col min="2" max="2" width="11" style="20" customWidth="1"/>
-    <col min="3" max="6" width="9.17188" style="20" customWidth="1"/>
-    <col min="7" max="7" width="9.85156" style="20" customWidth="1"/>
-    <col min="8" max="11" width="9.17188" style="20" customWidth="1"/>
-    <col min="12" max="16384" width="9.17188" style="20" customWidth="1"/>
+    <col min="1" max="1" width="2.67188" style="19" customWidth="1"/>
+    <col min="2" max="2" width="11" style="19" customWidth="1"/>
+    <col min="3" max="6" width="9.17188" style="19" customWidth="1"/>
+    <col min="7" max="7" width="9.85156" style="19" customWidth="1"/>
+    <col min="8" max="11" width="9.17188" style="19" customWidth="1"/>
+    <col min="12" max="16384" width="9.17188" style="19" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -18870,16 +19035,16 @@
       <c r="G3" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H3" s="14">
+      <c r="H3" s="13">
         <v>13</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="13">
         <v>12.36</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="13">
         <v>20</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="13">
         <v>547</v>
       </c>
     </row>
@@ -18905,16 +19070,16 @@
       <c r="G4" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="13">
         <v>12.54</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="13">
         <v>12.23</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="13">
         <v>16</v>
       </c>
-      <c r="K4" s="14">
+      <c r="K4" s="13">
         <v>547</v>
       </c>
     </row>
@@ -18940,16 +19105,16 @@
       <c r="G5" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="13">
         <v>12.49</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="13">
         <v>12.01</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="13">
         <v>39</v>
       </c>
-      <c r="K5" s="14">
+      <c r="K5" s="13">
         <v>544</v>
       </c>
     </row>
@@ -18975,16 +19140,16 @@
       <c r="G6" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="13">
         <v>12.55</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="13">
         <v>12.27</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="13">
         <v>21</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="13">
         <v>545</v>
       </c>
     </row>
@@ -19010,16 +19175,16 @@
       <c r="G7" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="13">
         <v>12.51</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="13">
         <v>12.21</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="13">
         <v>32</v>
       </c>
-      <c r="K7" s="14">
+      <c r="K7" s="13">
         <v>546</v>
       </c>
     </row>
@@ -19045,16 +19210,16 @@
       <c r="G8" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="13">
         <v>13</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="13">
         <v>12.12</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="13">
         <v>25</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="13">
         <v>549</v>
       </c>
     </row>
@@ -19080,16 +19245,16 @@
       <c r="G9" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="13">
         <v>12.56</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="13">
         <v>11.48</v>
       </c>
-      <c r="J9" s="14">
+      <c r="J9" s="13">
         <v>27</v>
       </c>
-      <c r="K9" s="14">
+      <c r="K9" s="13">
         <v>699</v>
       </c>
     </row>
@@ -19115,16 +19280,16 @@
       <c r="G10" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="13">
         <v>12.47</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="13">
         <v>12.15</v>
       </c>
-      <c r="J10" s="14">
+      <c r="J10" s="13">
         <v>16</v>
       </c>
-      <c r="K10" s="14">
+      <c r="K10" s="13">
         <v>699</v>
       </c>
     </row>
@@ -19150,16 +19315,16 @@
       <c r="G11" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="13">
         <v>12.5</v>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="13">
         <v>12.26</v>
       </c>
-      <c r="J11" s="14">
+      <c r="J11" s="13">
         <v>15</v>
       </c>
-      <c r="K11" s="14">
+      <c r="K11" s="13">
         <v>699</v>
       </c>
     </row>
@@ -19185,16 +19350,16 @@
       <c r="G12" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="13">
         <v>12.57</v>
       </c>
-      <c r="I12" s="14">
+      <c r="I12" s="13">
         <v>12.28</v>
       </c>
-      <c r="J12" s="14">
+      <c r="J12" s="13">
         <v>29</v>
       </c>
-      <c r="K12" s="14">
+      <c r="K12" s="13">
         <v>698</v>
       </c>
     </row>
@@ -19220,16 +19385,16 @@
       <c r="G13" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="13">
         <v>0.59</v>
       </c>
-      <c r="I13" s="14">
+      <c r="I13" s="13">
         <v>0.39</v>
       </c>
-      <c r="J13" s="14">
+      <c r="J13" s="13">
         <v>8</v>
       </c>
-      <c r="K13" s="14">
+      <c r="K13" s="13">
         <v>699</v>
       </c>
     </row>
@@ -19255,16 +19420,16 @@
       <c r="G14" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="13">
         <v>13</v>
       </c>
-      <c r="I14" s="14">
+      <c r="I14" s="13">
         <v>12.31</v>
       </c>
-      <c r="J14" s="14">
+      <c r="J14" s="13">
         <v>25</v>
       </c>
-      <c r="K14" s="14">
+      <c r="K14" s="13">
         <v>697</v>
       </c>
     </row>
@@ -19290,16 +19455,16 @@
       <c r="G15" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H15" s="13">
         <v>12.5</v>
       </c>
-      <c r="I15" s="14">
+      <c r="I15" s="13">
         <v>12.07</v>
       </c>
-      <c r="J15" s="14">
+      <c r="J15" s="13">
         <v>38</v>
       </c>
-      <c r="K15" s="14">
+      <c r="K15" s="13">
         <v>699</v>
       </c>
     </row>
@@ -19325,16 +19490,16 @@
       <c r="G16" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="13">
         <v>12.5</v>
       </c>
-      <c r="I16" s="14">
+      <c r="I16" s="13">
         <v>12.08</v>
       </c>
-      <c r="J16" s="14">
+      <c r="J16" s="13">
         <v>22</v>
       </c>
-      <c r="K16" s="14">
+      <c r="K16" s="13">
         <v>698</v>
       </c>
     </row>
@@ -19360,16 +19525,16 @@
       <c r="G17" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H17" s="14">
+      <c r="H17" s="13">
         <v>12.54</v>
       </c>
-      <c r="I17" s="14">
+      <c r="I17" s="13">
         <v>12.38</v>
       </c>
-      <c r="J17" s="14">
+      <c r="J17" s="13">
         <v>14</v>
       </c>
-      <c r="K17" s="14">
+      <c r="K17" s="13">
         <v>699</v>
       </c>
     </row>
@@ -19395,16 +19560,16 @@
       <c r="G18" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H18" s="13">
         <v>12.56</v>
       </c>
-      <c r="I18" s="14">
+      <c r="I18" s="13">
         <v>12.17</v>
       </c>
-      <c r="J18" s="14">
+      <c r="J18" s="13">
         <v>32</v>
       </c>
-      <c r="K18" s="14">
+      <c r="K18" s="13">
         <v>699</v>
       </c>
     </row>
@@ -19430,16 +19595,16 @@
       <c r="G19" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H19" s="13">
         <v>11.51</v>
       </c>
-      <c r="I19" s="14">
+      <c r="I19" s="13">
         <v>10.25</v>
       </c>
-      <c r="J19" s="14">
+      <c r="J19" s="13">
         <v>46</v>
       </c>
-      <c r="K19" s="14">
+      <c r="K19" s="13">
         <v>699</v>
       </c>
     </row>
@@ -19465,16 +19630,16 @@
       <c r="G20" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="13">
         <v>13</v>
       </c>
-      <c r="I20" s="14">
+      <c r="I20" s="13">
         <v>12.03</v>
       </c>
-      <c r="J20" s="14">
+      <c r="J20" s="13">
         <v>26</v>
       </c>
-      <c r="K20" s="14">
+      <c r="K20" s="13">
         <v>610</v>
       </c>
     </row>
@@ -19500,16 +19665,16 @@
       <c r="G21" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H21" s="13">
         <v>13</v>
       </c>
-      <c r="I21" s="14">
+      <c r="I21" s="13">
         <v>11.53</v>
       </c>
-      <c r="J21" s="14">
+      <c r="J21" s="13">
         <v>41</v>
       </c>
-      <c r="K21" s="14">
+      <c r="K21" s="13">
         <v>604</v>
       </c>
     </row>
@@ -19535,16 +19700,16 @@
       <c r="G22" t="s" s="9">
         <v>9</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H22" s="13">
         <v>13</v>
       </c>
-      <c r="I22" s="14">
+      <c r="I22" s="13">
         <v>12.02</v>
       </c>
-      <c r="J22" s="14">
+      <c r="J22" s="13">
         <v>34</v>
       </c>
-      <c r="K22" s="14">
+      <c r="K22" s="13">
         <v>542</v>
       </c>
     </row>
@@ -19570,16 +19735,16 @@
       <c r="G23" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H23" s="14">
+      <c r="H23" s="13">
         <v>13</v>
       </c>
-      <c r="I23" s="14">
+      <c r="I23" s="13">
         <v>12.41</v>
       </c>
-      <c r="J23" s="14">
-        <v>12</v>
-      </c>
-      <c r="K23" s="14">
+      <c r="J23" s="13">
+        <v>12</v>
+      </c>
+      <c r="K23" s="13">
         <v>549</v>
       </c>
     </row>
@@ -19605,16 +19770,16 @@
       <c r="G24" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H24" s="14">
+      <c r="H24" s="13">
         <v>13</v>
       </c>
-      <c r="I24" s="14">
+      <c r="I24" s="13">
         <v>12.22</v>
       </c>
-      <c r="J24" s="14">
+      <c r="J24" s="13">
         <v>13</v>
       </c>
-      <c r="K24" s="14">
+      <c r="K24" s="13">
         <v>546</v>
       </c>
     </row>
@@ -19640,16 +19805,16 @@
       <c r="G25" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H25" s="14">
+      <c r="H25" s="13">
         <v>13</v>
       </c>
-      <c r="I25" s="14">
+      <c r="I25" s="13">
         <v>11.53</v>
       </c>
-      <c r="J25" s="14">
+      <c r="J25" s="13">
         <v>28</v>
       </c>
-      <c r="K25" s="14">
+      <c r="K25" s="13">
         <v>698</v>
       </c>
     </row>
@@ -19675,16 +19840,16 @@
       <c r="G26" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H26" s="14">
+      <c r="H26" s="13">
         <v>12.44</v>
       </c>
-      <c r="I26" s="14">
+      <c r="I26" s="13">
         <v>11.35</v>
       </c>
-      <c r="J26" s="14">
+      <c r="J26" s="13">
         <v>39</v>
       </c>
-      <c r="K26" s="14">
+      <c r="K26" s="13">
         <v>699</v>
       </c>
     </row>
@@ -19710,16 +19875,16 @@
       <c r="G27" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H27" s="14">
+      <c r="H27" s="13">
         <v>12.49</v>
       </c>
-      <c r="I27" s="14">
+      <c r="I27" s="13">
         <v>11.54</v>
       </c>
-      <c r="J27" s="14">
+      <c r="J27" s="13">
         <v>22</v>
       </c>
-      <c r="K27" s="14">
+      <c r="K27" s="13">
         <v>699</v>
       </c>
     </row>
@@ -19745,16 +19910,16 @@
       <c r="G28" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H28" s="14">
+      <c r="H28" s="13">
         <v>12.45</v>
       </c>
-      <c r="I28" s="14">
+      <c r="I28" s="13">
         <v>11.1</v>
       </c>
-      <c r="J28" s="14">
+      <c r="J28" s="13">
         <v>44</v>
       </c>
-      <c r="K28" s="14">
+      <c r="K28" s="13">
         <v>698</v>
       </c>
     </row>
@@ -19780,16 +19945,16 @@
       <c r="G29" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H29" s="14">
+      <c r="H29" s="13">
         <v>13</v>
       </c>
-      <c r="I29" s="14">
+      <c r="I29" s="13">
         <v>12.05</v>
       </c>
-      <c r="J29" s="14">
+      <c r="J29" s="13">
         <v>27</v>
       </c>
-      <c r="K29" s="14">
+      <c r="K29" s="13">
         <v>699</v>
       </c>
     </row>
@@ -19815,16 +19980,16 @@
       <c r="G30" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H30" s="14">
+      <c r="H30" s="13">
         <v>12.45</v>
       </c>
-      <c r="I30" s="14">
+      <c r="I30" s="13">
         <v>12.02</v>
       </c>
-      <c r="J30" s="14">
+      <c r="J30" s="13">
         <v>28</v>
       </c>
-      <c r="K30" s="14">
+      <c r="K30" s="13">
         <v>699</v>
       </c>
     </row>
@@ -19846,12 +20011,12 @@
   <dimension ref="A1:K30"/>
   <sheetFormatPr defaultColWidth="9.16667" defaultRowHeight="15.4" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9.17188" style="21" customWidth="1"/>
-    <col min="2" max="2" width="11" style="21" customWidth="1"/>
-    <col min="3" max="6" width="9.17188" style="21" customWidth="1"/>
-    <col min="7" max="7" width="9.85156" style="21" customWidth="1"/>
-    <col min="8" max="11" width="9.17188" style="21" customWidth="1"/>
-    <col min="12" max="16384" width="9.17188" style="21" customWidth="1"/>
+    <col min="1" max="1" width="9.17188" style="20" customWidth="1"/>
+    <col min="2" max="2" width="11" style="20" customWidth="1"/>
+    <col min="3" max="6" width="9.17188" style="20" customWidth="1"/>
+    <col min="7" max="7" width="9.85156" style="20" customWidth="1"/>
+    <col min="8" max="11" width="9.17188" style="20" customWidth="1"/>
+    <col min="12" max="16384" width="9.17188" style="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -19928,16 +20093,16 @@
       <c r="G3" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H3" s="14">
+      <c r="H3" s="13">
         <v>13</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="13">
         <v>12.43</v>
       </c>
-      <c r="J3" s="14">
-        <v>11</v>
-      </c>
-      <c r="K3" s="14">
+      <c r="J3" s="13">
+        <v>11</v>
+      </c>
+      <c r="K3" s="13">
         <v>547</v>
       </c>
     </row>
@@ -19963,16 +20128,16 @@
       <c r="G4" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="13">
         <v>13</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="13">
         <v>12.52</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="13">
         <v>9</v>
       </c>
-      <c r="K4" s="14">
+      <c r="K4" s="13">
         <v>547</v>
       </c>
     </row>
@@ -19998,16 +20163,16 @@
       <c r="G5" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="13">
         <v>12.59</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="13">
         <v>12.35</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="13">
         <v>28</v>
       </c>
-      <c r="K5" s="14">
+      <c r="K5" s="13">
         <v>544</v>
       </c>
     </row>
@@ -20033,16 +20198,16 @@
       <c r="G6" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="13">
         <v>13</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="13">
         <v>12.4</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="13">
         <v>18</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="13">
         <v>545</v>
       </c>
     </row>
@@ -20068,16 +20233,16 @@
       <c r="G7" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="13">
         <v>12.45</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="13">
         <v>12.2</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="13">
         <v>14</v>
       </c>
-      <c r="K7" s="14">
+      <c r="K7" s="13">
         <v>546</v>
       </c>
     </row>
@@ -20103,16 +20268,16 @@
       <c r="G8" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="13">
         <v>12.56</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="13">
         <v>12.21</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="13">
         <v>27</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="13">
         <v>549</v>
       </c>
     </row>
@@ -20138,16 +20303,16 @@
       <c r="G9" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="13">
         <v>12.55</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="13">
         <v>12.23</v>
       </c>
-      <c r="J9" s="14">
+      <c r="J9" s="13">
         <v>15</v>
       </c>
-      <c r="K9" s="14">
+      <c r="K9" s="13">
         <v>699</v>
       </c>
     </row>
@@ -20173,16 +20338,16 @@
       <c r="G10" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="13">
         <v>13</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="13">
         <v>12.21</v>
       </c>
-      <c r="J10" s="14">
+      <c r="J10" s="13">
         <v>16</v>
       </c>
-      <c r="K10" s="14">
+      <c r="K10" s="13">
         <v>699</v>
       </c>
     </row>
@@ -20208,16 +20373,16 @@
       <c r="G11" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="13">
         <v>13</v>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="13">
         <v>12.33</v>
       </c>
-      <c r="J11" s="14">
+      <c r="J11" s="13">
         <v>23</v>
       </c>
-      <c r="K11" s="14">
+      <c r="K11" s="13">
         <v>699</v>
       </c>
     </row>
@@ -20243,16 +20408,16 @@
       <c r="G12" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="13">
         <v>13</v>
       </c>
-      <c r="I12" s="14">
+      <c r="I12" s="13">
         <v>11.37</v>
       </c>
-      <c r="J12" s="14">
+      <c r="J12" s="13">
         <v>38</v>
       </c>
-      <c r="K12" s="14">
+      <c r="K12" s="13">
         <v>698</v>
       </c>
     </row>
@@ -20278,16 +20443,16 @@
       <c r="G13" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="13">
         <v>13</v>
       </c>
-      <c r="I13" s="14">
+      <c r="I13" s="13">
         <v>11.47</v>
       </c>
-      <c r="J13" s="14">
+      <c r="J13" s="13">
         <v>36</v>
       </c>
-      <c r="K13" s="14">
+      <c r="K13" s="13">
         <v>699</v>
       </c>
     </row>
@@ -20313,16 +20478,16 @@
       <c r="G14" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="13">
         <v>13</v>
       </c>
-      <c r="I14" s="14">
+      <c r="I14" s="13">
         <v>12.17</v>
       </c>
-      <c r="J14" s="14">
+      <c r="J14" s="13">
         <v>46</v>
       </c>
-      <c r="K14" s="14">
+      <c r="K14" s="13">
         <v>697</v>
       </c>
     </row>
@@ -20348,16 +20513,16 @@
       <c r="G15" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H15" s="13">
         <v>13</v>
       </c>
-      <c r="I15" s="14">
+      <c r="I15" s="13">
         <v>12.14</v>
       </c>
-      <c r="J15" s="14">
+      <c r="J15" s="13">
         <v>43</v>
       </c>
-      <c r="K15" s="14">
+      <c r="K15" s="13">
         <v>699</v>
       </c>
     </row>
@@ -20383,16 +20548,16 @@
       <c r="G16" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="13">
         <v>13</v>
       </c>
-      <c r="I16" s="14">
+      <c r="I16" s="13">
         <v>12.12</v>
       </c>
-      <c r="J16" s="14">
+      <c r="J16" s="13">
         <v>40</v>
       </c>
-      <c r="K16" s="14">
+      <c r="K16" s="13">
         <v>698</v>
       </c>
     </row>
@@ -20418,16 +20583,16 @@
       <c r="G17" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H17" s="14">
+      <c r="H17" s="13">
         <v>13</v>
       </c>
-      <c r="I17" s="14">
+      <c r="I17" s="13">
         <v>12.24</v>
       </c>
-      <c r="J17" s="14">
+      <c r="J17" s="13">
         <v>24</v>
       </c>
-      <c r="K17" s="14">
+      <c r="K17" s="13">
         <v>699</v>
       </c>
     </row>
@@ -20453,16 +20618,16 @@
       <c r="G18" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H18" s="13">
         <v>12.53</v>
       </c>
-      <c r="I18" s="14">
+      <c r="I18" s="13">
         <v>12.04</v>
       </c>
-      <c r="J18" s="14">
+      <c r="J18" s="13">
         <v>28</v>
       </c>
-      <c r="K18" s="14">
+      <c r="K18" s="13">
         <v>699</v>
       </c>
     </row>
@@ -20488,16 +20653,16 @@
       <c r="G19" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H19" s="13">
         <v>12.57</v>
       </c>
-      <c r="I19" s="14">
+      <c r="I19" s="13">
         <v>11.58</v>
       </c>
-      <c r="J19" s="14">
+      <c r="J19" s="13">
         <v>25</v>
       </c>
-      <c r="K19" s="14">
+      <c r="K19" s="13">
         <v>699</v>
       </c>
     </row>
@@ -20523,16 +20688,16 @@
       <c r="G20" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="13">
         <v>12.58</v>
       </c>
-      <c r="I20" s="14">
+      <c r="I20" s="13">
         <v>12.19</v>
       </c>
-      <c r="J20" s="14">
+      <c r="J20" s="13">
         <v>27</v>
       </c>
-      <c r="K20" s="14">
+      <c r="K20" s="13">
         <v>610</v>
       </c>
     </row>
@@ -20558,16 +20723,16 @@
       <c r="G21" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H21" s="13">
         <v>12.58</v>
       </c>
-      <c r="I21" s="14">
+      <c r="I21" s="13">
         <v>10.56</v>
       </c>
-      <c r="J21" s="14">
+      <c r="J21" s="13">
         <v>89</v>
       </c>
-      <c r="K21" s="14">
+      <c r="K21" s="13">
         <v>604</v>
       </c>
     </row>
@@ -20593,16 +20758,16 @@
       <c r="G22" t="s" s="9">
         <v>9</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H22" s="13">
         <v>13</v>
       </c>
-      <c r="I22" s="14">
+      <c r="I22" s="13">
         <v>12.18</v>
       </c>
-      <c r="J22" s="14">
+      <c r="J22" s="13">
         <v>27</v>
       </c>
-      <c r="K22" s="14">
+      <c r="K22" s="13">
         <v>542</v>
       </c>
     </row>
@@ -20628,16 +20793,16 @@
       <c r="G23" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H23" s="14">
+      <c r="H23" s="13">
         <v>13</v>
       </c>
-      <c r="I23" s="14">
+      <c r="I23" s="13">
         <v>12.42</v>
       </c>
-      <c r="J23" s="14">
-        <v>11</v>
-      </c>
-      <c r="K23" s="14">
+      <c r="J23" s="13">
+        <v>11</v>
+      </c>
+      <c r="K23" s="13">
         <v>549</v>
       </c>
     </row>
@@ -20663,16 +20828,16 @@
       <c r="G24" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H24" s="14">
+      <c r="H24" s="13">
         <v>13</v>
       </c>
-      <c r="I24" s="14">
+      <c r="I24" s="13">
         <v>12.33</v>
       </c>
-      <c r="J24" s="14">
+      <c r="J24" s="13">
         <v>8</v>
       </c>
-      <c r="K24" s="14">
+      <c r="K24" s="13">
         <v>546</v>
       </c>
     </row>
@@ -20698,16 +20863,16 @@
       <c r="G25" t="s" s="9">
         <v>12</v>
       </c>
-      <c r="H25" s="14">
+      <c r="H25" s="13">
         <v>12.51</v>
       </c>
-      <c r="I25" s="14">
+      <c r="I25" s="13">
         <v>12.14</v>
       </c>
-      <c r="J25" s="14">
+      <c r="J25" s="13">
         <v>34</v>
       </c>
-      <c r="K25" s="14">
+      <c r="K25" s="13">
         <v>698</v>
       </c>
     </row>
@@ -20733,16 +20898,16 @@
       <c r="G26" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H26" s="14">
+      <c r="H26" s="13">
         <v>13</v>
       </c>
-      <c r="I26" s="14">
+      <c r="I26" s="13">
         <v>12.24</v>
       </c>
-      <c r="J26" s="14">
+      <c r="J26" s="13">
         <v>33</v>
       </c>
-      <c r="K26" s="14">
+      <c r="K26" s="13">
         <v>699</v>
       </c>
     </row>
@@ -20768,16 +20933,16 @@
       <c r="G27" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H27" s="14">
+      <c r="H27" s="13">
         <v>12.55</v>
       </c>
-      <c r="I27" s="14">
+      <c r="I27" s="13">
         <v>12.01</v>
       </c>
-      <c r="J27" s="14">
+      <c r="J27" s="13">
         <v>34</v>
       </c>
-      <c r="K27" s="14">
+      <c r="K27" s="13">
         <v>699</v>
       </c>
     </row>
@@ -20803,16 +20968,16 @@
       <c r="G28" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H28" s="14">
+      <c r="H28" s="13">
         <v>13</v>
       </c>
-      <c r="I28" s="14">
+      <c r="I28" s="13">
         <v>11.11</v>
       </c>
-      <c r="J28" s="14">
+      <c r="J28" s="13">
         <v>61</v>
       </c>
-      <c r="K28" s="14">
+      <c r="K28" s="13">
         <v>698</v>
       </c>
     </row>
@@ -20838,16 +21003,16 @@
       <c r="G29" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H29" s="14">
+      <c r="H29" s="13">
         <v>13</v>
       </c>
-      <c r="I29" s="14">
+      <c r="I29" s="13">
         <v>11.26</v>
       </c>
-      <c r="J29" s="14">
+      <c r="J29" s="13">
         <v>61</v>
       </c>
-      <c r="K29" s="14">
+      <c r="K29" s="13">
         <v>699</v>
       </c>
     </row>
@@ -20873,16 +21038,16 @@
       <c r="G30" t="s" s="9">
         <v>10</v>
       </c>
-      <c r="H30" s="14">
+      <c r="H30" s="13">
         <v>12.59</v>
       </c>
-      <c r="I30" s="14">
+      <c r="I30" s="13">
         <v>11.18</v>
       </c>
-      <c r="J30" s="14">
+      <c r="J30" s="13">
         <v>60</v>
       </c>
-      <c r="K30" s="14">
+      <c r="K30" s="13">
         <v>699</v>
       </c>
     </row>
@@ -20904,16 +21069,16 @@
   <dimension ref="A1:K30"/>
   <sheetFormatPr defaultColWidth="9.16667" defaultRowHeight="15.4" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9.17188" style="22" customWidth="1"/>
-    <col min="2" max="2" width="11" style="22" customWidth="1"/>
-    <col min="3" max="6" width="9.17188" style="22" customWidth="1"/>
-    <col min="7" max="7" width="9.85156" style="22" customWidth="1"/>
-    <col min="8" max="11" width="9.17188" style="22" customWidth="1"/>
-    <col min="12" max="16384" width="9.17188" style="22" customWidth="1"/>
+    <col min="1" max="1" width="9.17188" style="21" customWidth="1"/>
+    <col min="2" max="2" width="11" style="21" customWidth="1"/>
+    <col min="3" max="6" width="9.17188" style="21" customWidth="1"/>
+    <col min="7" max="7" width="9.85156" style="21" customWidth="1"/>
+    <col min="8" max="11" width="9.17188" style="21" customWidth="1"/>
+    <col min="12" max="16384" width="9.17188" style="21" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="23"/>
+      <c r="A1" s="22"/>
       <c r="B1" t="s" s="3">
         <v>0</v>
       </c>
